--- a/Kq_Thuật_toán_AI_Bảng.xlsx
+++ b/Kq_Thuật_toán_AI_Bảng.xlsx
@@ -1570,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U281"/>
+  <dimension ref="A1:U435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1636,37 +1636,37 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 296.97 ms</t>
+          <t>Thời gian: 294.98 ms</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 435.18 ms</t>
+          <t>Thời gian: 437.49 ms</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 428.06 ms</t>
+          <t>Thời gian: 394.58 ms</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 275.15 ms</t>
+          <t>Thời gian: 261.58 ms</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 696.95 ms</t>
+          <t>Thời gian: 705.63 ms</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 460.89 ms</t>
+          <t>Thời gian: 652.48 ms</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 277.57 ms</t>
+          <t>Thời gian: 280.47 ms</t>
         </is>
       </c>
     </row>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>216024.2017392527</v>
+        <v>216024.7519830532</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>14</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>216023.6512298374</v>
+        <v>216024.2015556349</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>15</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>216023.1007778175</v>
+        <v>216023.6512298374</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>16</v>
@@ -3159,11 +3159,11 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>216022.55055</v>
+        <v>216023.1007778175</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>17</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>216022</v>
+        <v>216022.55055</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>18</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -3317,11 +3317,11 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>215022.1011</v>
+        <v>216022</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>19</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>215021.55055</v>
+        <v>216022.1007778175</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>20</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
@@ -3475,11 +3475,11 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>215021</v>
+        <v>216021.55055</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>21</v>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>215021.1007778175</v>
+        <v>216021</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>22</v>
@@ -3622,22 +3622,22 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>215022.7522677081</v>
+        <v>215021.65165</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>215020.55055</v>
+        <v>215022.7522677081</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>23</v>
@@ -3705,18 +3705,18 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>215022.2017392527</v>
+        <v>215021.1011</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>215020</v>
+        <v>215022.2017392527</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>24</v>
@@ -3780,11 +3780,11 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>215021.65165</v>
+        <v>215020.55055</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>214023.4031112698</v>
+        <v>215021.65165</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>25</v>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>215021.1011</v>
+        <v>215020</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>26</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>214022.85275</v>
+        <v>215021.1011</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>26</v>
@@ -3938,11 +3938,11 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>215020.55055</v>
+        <v>214022.3022</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>27</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>214022.3024596748</v>
+        <v>215020.55055</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>27</v>
@@ -4017,11 +4017,11 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>215020</v>
+        <v>214021.75165</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>214021.7522677081</v>
+        <v>215020</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>28</v>
@@ -4096,22 +4096,22 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>214022.3022</v>
+        <v>214021.2011</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>214021.2017392527</v>
+        <v>214022.3022</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>29</v>
@@ -4175,22 +4175,22 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>214021.75165</v>
+        <v>214020.6512298374</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>214020.6512298374</v>
+        <v>214021.7522677081</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>30</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>214021.2011</v>
+        <v>214020.1007778175</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>31</v>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="L35" s="4" t="n">
-        <v>214020.1007778175</v>
+        <v>214021.2017392527</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>31</v>
@@ -4333,11 +4333,11 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>214020.6512298374</v>
+        <v>214019.55055</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>32</v>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>214019.55055</v>
+        <v>214020.6512298374</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>32</v>
@@ -4412,22 +4412,22 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>214020.1007778175</v>
+        <v>214019</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L37" s="4" t="n">
-        <v>214019</v>
+        <v>214020.1007778175</v>
       </c>
       <c r="M37" s="4" t="n">
         <v>33</v>
@@ -4491,22 +4491,22 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>214019.55055</v>
+        <v>213021.3023334524</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>213021.3023334524</v>
+        <v>214019.55055</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>34</v>
@@ -4570,22 +4570,22 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>214019</v>
+        <v>213020.7519830532</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L39" s="4" t="n">
-        <v>213020.7519830532</v>
+        <v>214019</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>35</v>
@@ -4649,22 +4649,22 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>213021.3023334524</v>
+        <v>213020.2017392527</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>213020.2017392527</v>
+        <v>213021.3023334524</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>36</v>
@@ -4728,22 +4728,22 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>213020.7519830532</v>
+        <v>213019.6512298374</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L41" s="4" t="n">
-        <v>213019.6512298374</v>
+        <v>213020.7519830532</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>37</v>
@@ -4807,11 +4807,11 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>213020.2017392527</v>
+        <v>213019.1007778175</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>38</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>213019.1007778175</v>
+        <v>213020.2015556349</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>38</v>
@@ -4886,22 +4886,22 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>213019.6512298374</v>
+        <v>213018.55055</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L43" s="4" t="n">
-        <v>213018.55055</v>
+        <v>213019.6512298374</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>39</v>
@@ -4969,18 +4969,18 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>213019.1007778175</v>
+        <v>213018</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>213018</v>
+        <v>213019.1007778175</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>40</v>
@@ -5044,11 +5044,11 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>213018.55055</v>
+        <v>212020.3024596748</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>41</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="L45" s="4" t="n">
-        <v>212020.3024596748</v>
+        <v>213018.55055</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>41</v>
@@ -5123,11 +5123,11 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>213018</v>
+        <v>212019.7519830532</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>42</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>212019.7522677081</v>
+        <v>213018</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>42</v>
@@ -5202,11 +5202,11 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>212020.3024596748</v>
+        <v>212019.2017392527</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>43</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="L47" s="4" t="n">
-        <v>212019.7519830532</v>
+        <v>212020.3024596748</v>
       </c>
       <c r="M47" s="4" t="n">
         <v>43</v>
@@ -5281,22 +5281,22 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>212019.7519830532</v>
+        <v>212018.65165</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>212019.2017392527</v>
+        <v>212019.7519830532</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>44</v>
@@ -5364,18 +5364,18 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>212019.2015556349</v>
+        <v>212018.1011</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L49" s="4" t="n">
-        <v>212018.65165</v>
+        <v>212019.2017392527</v>
       </c>
       <c r="M49" s="4" t="n">
         <v>45</v>
@@ -5439,11 +5439,11 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>212018.6512298374</v>
+        <v>212017.55055</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>46</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>212018.1011</v>
+        <v>212018.65165</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>46</v>
@@ -5518,22 +5518,22 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>212018.1011</v>
+        <v>212017</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L51" s="4" t="n">
-        <v>212017.55055</v>
+        <v>212018.1011</v>
       </c>
       <c r="M51" s="4" t="n">
         <v>47</v>
@@ -5597,22 +5597,22 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>212017.55055</v>
+        <v>211019.85275</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>212017</v>
+        <v>212017.55055</v>
       </c>
       <c r="M52" s="4" t="n">
         <v>48</v>
@@ -5680,18 +5680,18 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>212017</v>
+        <v>211019.3023334524</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L53" s="4" t="n">
-        <v>212016</v>
+        <v>212017</v>
       </c>
       <c r="M53" s="4" t="n">
         <v>49</v>
@@ -5755,22 +5755,22 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>211019.85275</v>
+        <v>211018.7519830532</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>212015</v>
+        <v>211019.85275</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>50</v>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>211019.3023334524</v>
+        <v>211018.2015556349</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L55" s="4" t="n">
-        <v>211015.65165</v>
+        <v>211019.3023334524</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>51</v>
@@ -5917,18 +5917,18 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>211018.7519830532</v>
+        <v>211017.6512298374</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>211015.1011</v>
+        <v>211018.7519830532</v>
       </c>
       <c r="M56" s="4" t="n">
         <v>52</v>
@@ -5992,22 +5992,22 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>211018.2017392527</v>
+        <v>211017.1007778175</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L57" s="4" t="n">
-        <v>211014.55055</v>
+        <v>211018.2015556349</v>
       </c>
       <c r="M57" s="4" t="n">
         <v>53</v>
@@ -6075,18 +6075,18 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>211017.6512298374</v>
+        <v>211016.55055</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>211014</v>
+        <v>211017.6512298374</v>
       </c>
       <c r="M58" s="4" t="n">
         <v>54</v>
@@ -6150,22 +6150,22 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>211017.1007778175</v>
+        <v>211016</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L59" s="4" t="n">
-        <v>210015.7522677081</v>
+        <v>211017.1007778175</v>
       </c>
       <c r="M59" s="4" t="n">
         <v>55</v>
@@ -6229,22 +6229,22 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>211016.55055</v>
+        <v>210019.4031112698</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>210015.2017392527</v>
+        <v>211016.55055</v>
       </c>
       <c r="M60" s="4" t="n">
         <v>56</v>
@@ -6308,22 +6308,22 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>211016</v>
+        <v>210018.85275</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>210014.65165</v>
+        <v>211016</v>
       </c>
       <c r="M61" s="4" t="n">
         <v>57</v>
@@ -6387,22 +6387,22 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>210019.4031112698</v>
+        <v>210018.3024596748</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>210014.1011</v>
+        <v>210019.4031112698</v>
       </c>
       <c r="M62" s="4" t="n">
         <v>58</v>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>210018.85275</v>
+        <v>210017.7519830532</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>59</v>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="L63" s="4" t="n">
-        <v>210013.55055</v>
+        <v>210018.85275</v>
       </c>
       <c r="M63" s="4" t="n">
         <v>59</v>
@@ -6549,18 +6549,18 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>210018.3024596748</v>
+        <v>210017.2015556349</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>60</v>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>210013</v>
+        <v>210018.3023334524</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>60</v>
@@ -6628,18 +6628,18 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>210017.7522677081</v>
+        <v>210016.6512298374</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L65" s="4" t="n">
-        <v>209016.4034785054</v>
+        <v>210017.7519830532</v>
       </c>
       <c r="M65" s="4" t="n">
         <v>61</v>
@@ -6703,11 +6703,11 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>210017.2017392527</v>
+        <v>210016.1011</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>62</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>209015.8529618406</v>
+        <v>210017.2015556349</v>
       </c>
       <c r="M66" s="4" t="n">
         <v>62</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>210016.6512298374</v>
+        <v>210015.55055</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>63</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="L67" s="4" t="n">
-        <v>209015.3024596748</v>
+        <v>210016.6512298374</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>63</v>
@@ -6861,22 +6861,22 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>210016.1011</v>
+        <v>210015</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>64</v>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>209014.7522677081</v>
+        <v>210016.1011</v>
       </c>
       <c r="M68" s="4" t="n">
         <v>64</v>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>210015.55055</v>
+        <v>209022.2572341205</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>65</v>
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="L69" s="4" t="n">
-        <v>209014.7519830532</v>
+        <v>210015.55055</v>
       </c>
       <c r="M69" s="4" t="n">
         <v>65</v>
@@ -7019,11 +7019,11 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>210015</v>
+        <v>209021.7071711227</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>66</v>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>209014.2015556349</v>
+        <v>210015</v>
       </c>
       <c r="M70" s="4" t="n">
         <v>66</v>
@@ -7102,18 +7102,18 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>209022.2572341205</v>
+        <v>209021.156622877</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>67</v>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L71" s="4" t="n">
-        <v>209013.6512298374</v>
+        <v>209022.2572341205</v>
       </c>
       <c r="M71" s="4" t="n">
         <v>67</v>
@@ -7177,22 +7177,22 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>209021.7071711227</v>
+        <v>209020.6060749486</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>209013.1011</v>
+        <v>209021.7071711227</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>68</v>
@@ -7260,18 +7260,18 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>209021.7062709648</v>
+        <v>209020.6052177582</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L73" s="4" t="n">
-        <v>9013</v>
+        <v>209021.7062709648</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>69</v>
@@ -7335,11 +7335,11 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>209021.156149187</v>
+        <v>209020.0546992021</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>70</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>9012</v>
+        <v>209021.156149187</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>70</v>
@@ -7414,11 +7414,11 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>209020.6056089214</v>
+        <v>209019.5045354162</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>71</v>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="L75" s="4" t="n">
-        <v>9011</v>
+        <v>209020.6060749486</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>71</v>
@@ -7497,18 +7497,18 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>209020.0550707495</v>
+        <v>209018.9540040604</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>72</v>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>9011.100777817459</v>
+        <v>209020.0555274316</v>
       </c>
       <c r="M76" s="4" t="n">
         <v>72</v>
@@ -7576,18 +7576,18 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>209019.5045354162</v>
+        <v>209018.4034785054</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>73</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L77" s="4" t="n">
-        <v>9010.55055</v>
+        <v>209019.5049804618</v>
       </c>
       <c r="M77" s="4" t="n">
         <v>73</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>209018.9540040604</v>
+        <v>209017.8529618406</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>74</v>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>9010</v>
+        <v>209018.95495</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>74</v>
@@ -7730,11 +7730,11 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>209018.4034785054</v>
+        <v>209017.3028044607</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>75</v>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="L79" s="4" t="n">
-        <v>8012.302459674775</v>
+        <v>209018.4044</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>75</v>
@@ -7813,18 +7813,18 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>209017.8533455194</v>
+        <v>209016.75275</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>76</v>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>8011.751983053202</v>
+        <v>209017.85385</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>76</v>
@@ -7892,18 +7892,18 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>209017.3028044607</v>
+        <v>209016.2022</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>77</v>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L81" s="4" t="n">
-        <v>8011.201739252713</v>
+        <v>209017.3033</v>
       </c>
       <c r="M81" s="4" t="n">
         <v>77</v>
@@ -7971,18 +7971,18 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>209016.7522677081</v>
+        <v>209015.65165</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>78</v>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>8010.651650000001</v>
+        <v>209016.75275</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>78</v>
@@ -8050,18 +8050,18 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>209016.2017392527</v>
+        <v>209015.1011</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>79</v>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L83" s="4" t="n">
-        <v>8010.1011</v>
+        <v>209016.2022</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>79</v>
@@ -8125,22 +8125,22 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>209015.65165</v>
+        <v>209014.55055</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>80</v>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>8009.55055</v>
+        <v>209015.65165</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>80</v>
@@ -8208,18 +8208,18 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>209015.1011</v>
+        <v>209014</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>81</v>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L85" s="4" t="n">
-        <v>8009</v>
+        <v>209015.1011</v>
       </c>
       <c r="M85" s="4" t="n">
         <v>81</v>
@@ -8283,11 +8283,11 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>209014.55055</v>
+        <v>208015.2015556349</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>82</v>
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="L86" s="4" t="n">
-        <v>8008</v>
+        <v>209014.55055</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>82</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>209014</v>
+        <v>208014.6512298374</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>83</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="L87" s="4" t="n">
-        <v>7008.651229837387</v>
+        <v>209014</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>83</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>208015.2015556349</v>
+        <v>208014.1007778175</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>84</v>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="L88" s="4" t="n">
-        <v>7008.100777817459</v>
+        <v>208015.2015556349</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>84</v>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>208014.6512298374</v>
+        <v>208013.55055</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>85</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="L89" s="4" t="n">
-        <v>7007.55055</v>
+        <v>208014.6512298374</v>
       </c>
       <c r="M89" s="4" t="n">
         <v>85</v>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>208014.1007778175</v>
+        <v>208013</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>86</v>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="L90" s="4" t="n">
-        <v>7007</v>
+        <v>208014.1007778175</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>86</v>
@@ -8682,18 +8682,18 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>208013.55055</v>
+        <v>208012</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>87</v>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L91" s="4" t="n">
-        <v>6009.853345519392</v>
+        <v>208013.55055</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>87</v>
@@ -8757,22 +8757,22 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>208013</v>
+        <v>208011</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>88</v>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>6009.302804460733</v>
+        <v>208013</v>
       </c>
       <c r="M92" s="4" t="n">
         <v>88</v>
@@ -8840,18 +8840,18 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>208012</v>
+        <v>207011.65165</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>89</v>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L93" s="4" t="n">
-        <v>6008.752267708094</v>
+        <v>208012</v>
       </c>
       <c r="M93" s="4" t="n">
         <v>89</v>
@@ -8915,22 +8915,22 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>208011</v>
+        <v>207011.1011</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>90</v>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L94" s="4" t="n">
-        <v>6008.201739252713</v>
+        <v>208011</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>90</v>
@@ -8994,22 +8994,22 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>207011.65165</v>
+        <v>207010.55055</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>91</v>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L95" s="4" t="n">
-        <v>6007.651229837387</v>
+        <v>207011.65165</v>
       </c>
       <c r="M95" s="4" t="n">
         <v>91</v>
@@ -9077,18 +9077,18 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>207011.1011</v>
+        <v>207010</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>92</v>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L96" s="4" t="n">
-        <v>6007.100777817459</v>
+        <v>207011.1011</v>
       </c>
       <c r="M96" s="4" t="n">
         <v>92</v>
@@ -9152,22 +9152,22 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>207010.55055</v>
+        <v>206011.7522677081</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>93</v>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L97" s="4" t="n">
-        <v>6006.55055</v>
+        <v>207010.55055</v>
       </c>
       <c r="M97" s="4" t="n">
         <v>93</v>
@@ -9235,18 +9235,18 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>207010</v>
+        <v>206011.2017392527</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>94</v>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L98" s="4" t="n">
-        <v>6006</v>
+        <v>207010</v>
       </c>
       <c r="M98" s="4" t="n">
         <v>94</v>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>206011.7522677081</v>
+        <v>206010.6512298374</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>95</v>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L99" s="4" t="n">
-        <v>5006.651229837387</v>
+        <v>206011.7522677081</v>
       </c>
       <c r="M99" s="4" t="n">
         <v>95</v>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>206011.2017392527</v>
+        <v>206010.1007778175</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>96</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>5006.100777817459</v>
+        <v>206011.2017392527</v>
       </c>
       <c r="M100" s="4" t="n">
         <v>96</v>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>206010.65165</v>
+        <v>206009.55055</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>97</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="L101" s="4" t="n">
-        <v>5005.55055</v>
+        <v>206010.65165</v>
       </c>
       <c r="M101" s="4" t="n">
         <v>97</v>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>206010.1011</v>
+        <v>206009</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>98</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>5005</v>
+        <v>206010.1011</v>
       </c>
       <c r="M102" s="4" t="n">
         <v>98</v>
@@ -9626,22 +9626,22 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>206009.55055</v>
+        <v>205012.4034785054</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99</v>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L103" s="4" t="n">
-        <v>4012.806645675285</v>
+        <v>206009.55055</v>
       </c>
       <c r="M103" s="4" t="n">
         <v>99</v>
@@ -9709,18 +9709,18 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>206009</v>
+        <v>205012.4031112698</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>4012.256437584951</v>
+        <v>206009</v>
       </c>
       <c r="M104" s="4" t="n">
         <v>100</v>
@@ -9784,22 +9784,22 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>205012.4034785054</v>
+        <v>205011.85275</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>101</v>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L105" s="4" t="n">
-        <v>4011.706270964838</v>
+        <v>205012.4034785054</v>
       </c>
       <c r="M105" s="4" t="n">
         <v>101</v>
@@ -9867,18 +9867,18 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>205012.4031112698</v>
+        <v>205011.3024596748</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>102</v>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>4011.156149186938</v>
+        <v>205012.4031112698</v>
       </c>
       <c r="M106" s="4" t="n">
         <v>102</v>
@@ -9942,22 +9942,22 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>205011.85275</v>
+        <v>205010.7519830532</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>103</v>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
-        <v>4010.606074948559</v>
+        <v>205011.85275</v>
       </c>
       <c r="M107" s="4" t="n">
         <v>103</v>
@@ -10021,22 +10021,22 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>205011.3024596748</v>
+        <v>205010.2015556349</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>104</v>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>4010.055527431592</v>
+        <v>205011.3024596748</v>
       </c>
       <c r="M108" s="4" t="n">
         <v>104</v>
@@ -10100,22 +10100,22 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>205010.7519830532</v>
+        <v>205009.6512298374</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>105</v>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>4009.504980461826</v>
+        <v>205010.7519830532</v>
       </c>
       <c r="M109" s="4" t="n">
         <v>105</v>
@@ -10179,22 +10179,22 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>205010.2017392527</v>
+        <v>205009.1007778175</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>106</v>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>4008.954434241761</v>
+        <v>205010.2017392527</v>
       </c>
       <c r="M110" s="4" t="n">
         <v>106</v>
@@ -10262,18 +10262,18 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>205009.6512298374</v>
+        <v>205008.55055</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>107</v>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L111" s="4" t="n">
-        <v>4008.403889087297</v>
+        <v>205009.6512298374</v>
       </c>
       <c r="M111" s="4" t="n">
         <v>107</v>
@@ -10337,22 +10337,22 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>205009.1007778175</v>
+        <v>205008</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>108</v>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>4007.853345519391</v>
+        <v>205009.1007778175</v>
       </c>
       <c r="M112" s="4" t="n">
         <v>108</v>
@@ -10416,22 +10416,22 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>205008.55055</v>
+        <v>204009.7519830532</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>109</v>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L113" s="4" t="n">
-        <v>4007.302804460732</v>
+        <v>205008.55055</v>
       </c>
       <c r="M113" s="4" t="n">
         <v>109</v>
@@ -10495,22 +10495,22 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>205008</v>
+        <v>204009.2015556349</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>110</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>4006.752267708094</v>
+        <v>205008</v>
       </c>
       <c r="M114" s="4" t="n">
         <v>110</v>
@@ -10574,22 +10574,22 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>204009.7519830532</v>
+        <v>204008.6512298374</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>111</v>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
-        <v>4006.201739252713</v>
+        <v>204009.7519830532</v>
       </c>
       <c r="M115" s="4" t="n">
         <v>111</v>
@@ -10657,18 +10657,18 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>204009.2015556349</v>
+        <v>204008.1011</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>112</v>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>4005.651229837388</v>
+        <v>204009.2015556349</v>
       </c>
       <c r="M116" s="4" t="n">
         <v>112</v>
@@ -10736,18 +10736,18 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>204008.6512298374</v>
+        <v>204007.55055</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>113</v>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L117" s="4" t="n">
-        <v>4005.100777817459</v>
+        <v>204008.6512298374</v>
       </c>
       <c r="M117" s="4" t="n">
         <v>113</v>
@@ -10811,11 +10811,11 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>204008.1007778175</v>
+        <v>204007</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>114</v>
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>4004.55055</v>
+        <v>204008.1011</v>
       </c>
       <c r="M118" s="4" t="n">
         <v>114</v>
@@ -10890,11 +10890,11 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>204007.55055</v>
+        <v>3006</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>115</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="L119" s="4" t="n">
-        <v>4004</v>
+        <v>204007.55055</v>
       </c>
       <c r="M119" s="4" t="n">
         <v>115</v>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>204007</v>
+        <v>3005</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>116</v>
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>3006.85275</v>
+        <v>204007</v>
       </c>
       <c r="M120" s="4" t="n">
         <v>116</v>
@@ -11048,22 +11048,22 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>117</v>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>3006.302333452378</v>
+        <v>3006</v>
       </c>
       <c r="M121" s="4" t="n">
         <v>117</v>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>3005</v>
+        <v>3004.100777817459</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>118</v>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>3005.751983053201</v>
+        <v>3005</v>
       </c>
       <c r="M122" s="4" t="n">
         <v>118</v>
@@ -11206,22 +11206,22 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>3004</v>
+        <v>3003.55055</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>119</v>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L123" s="4" t="n">
-        <v>3005.201555634919</v>
+        <v>3004</v>
       </c>
       <c r="M123" s="4" t="n">
         <v>119</v>
@@ -11289,18 +11289,18 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>3004.100777817459</v>
+        <v>3003</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>120</v>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>3004.651229837388</v>
+        <v>3004.100777817459</v>
       </c>
       <c r="M124" s="4" t="n">
         <v>120</v>
@@ -11364,22 +11364,22 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>3003.55055</v>
+        <v>2008.054295637322</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>121</v>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L125" s="4" t="n">
-        <v>3004.100777817459</v>
+        <v>3003.55055</v>
       </c>
       <c r="M125" s="4" t="n">
         <v>121</v>
@@ -11443,22 +11443,22 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>3003</v>
+        <v>2007.503889087297</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>122</v>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>3003.55055</v>
+        <v>3003</v>
       </c>
       <c r="M126" s="4" t="n">
         <v>122</v>
@@ -11522,22 +11522,22 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2008.054295637322</v>
+        <v>2006.95352171833</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>123</v>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L127" s="4" t="n">
-        <v>3003</v>
+        <v>2008.054295637322</v>
       </c>
       <c r="M127" s="4" t="n">
         <v>123</v>
@@ -11605,18 +11605,18 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>2007.503889087297</v>
+        <v>2006.403111269837</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>124</v>
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>2006.403111269837</v>
+        <v>2007.503889087297</v>
       </c>
       <c r="M128" s="4" t="n">
         <v>124</v>
@@ -11684,18 +11684,18 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>2006.95352171833</v>
+        <v>2005.85275</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>125</v>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>2005.85275</v>
+        <v>2006.95352171833</v>
       </c>
       <c r="M129" s="4" t="n">
         <v>125</v>
@@ -11759,11 +11759,11 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>2006.403111269837</v>
+        <v>2005.302333452378</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>126</v>
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>2005.302459674775</v>
+        <v>2006.403111269837</v>
       </c>
       <c r="M130" s="4" t="n">
         <v>126</v>
@@ -11842,18 +11842,18 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>2005.85275</v>
+        <v>2004.751983053201</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>127</v>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>2004.752267708094</v>
+        <v>2005.85275</v>
       </c>
       <c r="M131" s="4" t="n">
         <v>127</v>
@@ -11921,18 +11921,18 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>2005.302333452378</v>
+        <v>2004.201555634919</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>128</v>
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>2004.201739252713</v>
+        <v>2005.302333452378</v>
       </c>
       <c r="M132" s="4" t="n">
         <v>128</v>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2004.751983053201</v>
+        <v>2003.651229837388</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>129</v>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>2003.65165</v>
+        <v>2004.751983053201</v>
       </c>
       <c r="M133" s="4" t="n">
         <v>129</v>
@@ -12075,11 +12075,11 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>2004.201555634919</v>
+        <v>2003.100777817459</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>130</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>2003.1011</v>
+        <v>2004.201555634919</v>
       </c>
       <c r="M134" s="4" t="n">
         <v>130</v>
@@ -12154,11 +12154,11 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>2003.651229837388</v>
+        <v>2002.55055</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>131</v>
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>2002.55055</v>
+        <v>2003.651229837388</v>
       </c>
       <c r="M135" s="4" t="n">
         <v>131</v>
@@ -12237,18 +12237,18 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2003.100777817459</v>
+        <v>2002</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>132</v>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L136" s="4" t="n">
-        <v>2002</v>
+        <v>2003.100777817459</v>
       </c>
       <c r="M136" s="4" t="n">
         <v>132</v>
@@ -12312,22 +12312,22 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2002.55055</v>
+        <v>1002.651229837388</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>133</v>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>1009.806645675285</v>
+        <v>2002.55055</v>
       </c>
       <c r="M137" s="4" t="n">
         <v>133</v>
@@ -12395,18 +12395,18 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2002</v>
+        <v>1002.100777817459</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>134</v>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>1009.256437584951</v>
+        <v>2002</v>
       </c>
       <c r="M138" s="4" t="n">
         <v>134</v>
@@ -12474,18 +12474,18 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>1002.651229837388</v>
+        <v>1001.55055</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>135</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>1008.705923681288</v>
+        <v>1002.651229837388</v>
       </c>
       <c r="M139" s="4" t="n">
         <v>135</v>
@@ -12549,22 +12549,22 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>1002.100777817459</v>
+        <v>1001</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>136</v>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>1008.15574216858</v>
+        <v>1002.1011</v>
       </c>
       <c r="M140" s="4" t="n">
         <v>136</v>
@@ -12628,22 +12628,22 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>1001.55055</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>137</v>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>1007.605217758139</v>
+        <v>1001.55055</v>
       </c>
       <c r="M141" s="4" t="n">
         <v>137</v>
@@ -12702,27 +12702,16 @@
       <c r="F142" s="4" t="n">
         <v>1010</v>
       </c>
-      <c r="G142" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="n">
-        <v>1001</v>
-      </c>
       <c r="J142" s="4" t="n">
         <v>138</v>
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L142" s="4" t="n">
-        <v>1007.05469920206</v>
+        <v>1001</v>
       </c>
       <c r="M142" s="4" t="n">
         <v>138</v>
@@ -12781,27 +12770,16 @@
       <c r="F143" s="4" t="n">
         <v>1009.5</v>
       </c>
-      <c r="G143" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J143" s="4" t="n">
         <v>139</v>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>1006.504535416188</v>
+        <v>0</v>
       </c>
       <c r="M143" s="4" t="n">
         <v>139</v>
@@ -12860,17 +12838,6 @@
       <c r="F144" s="4" t="n">
         <v>1009</v>
       </c>
-      <c r="J144" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="n">
-        <v>1005.954434241762</v>
-      </c>
       <c r="M144" s="4" t="n">
         <v>140</v>
       </c>
@@ -12928,17 +12895,6 @@
       <c r="F145" s="4" t="n">
         <v>1008.5</v>
       </c>
-      <c r="J145" s="4" t="n">
-        <v>141</v>
-      </c>
-      <c r="K145" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="L145" s="4" t="n">
-        <v>1005.4044</v>
-      </c>
       <c r="M145" s="4" t="n">
         <v>141</v>
       </c>
@@ -12996,17 +12952,6 @@
       <c r="F146" s="4" t="n">
         <v>1008</v>
       </c>
-      <c r="J146" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v>1004.85385</v>
-      </c>
       <c r="M146" s="4" t="n">
         <v>142</v>
       </c>
@@ -13064,17 +13009,6 @@
       <c r="F147" s="4" t="n">
         <v>1007.5</v>
       </c>
-      <c r="J147" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L147" s="4" t="n">
-        <v>1004.3033</v>
-      </c>
       <c r="M147" s="4" t="n">
         <v>143</v>
       </c>
@@ -13121,17 +13055,6 @@
       <c r="F148" s="4" t="n">
         <v>1007</v>
       </c>
-      <c r="J148" s="4" t="n">
-        <v>144</v>
-      </c>
-      <c r="K148" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L148" s="4" t="n">
-        <v>1003.75275</v>
-      </c>
       <c r="M148" s="4" t="n">
         <v>144</v>
       </c>
@@ -13167,17 +13090,6 @@
       <c r="F149" s="4" t="n">
         <v>1006.5</v>
       </c>
-      <c r="J149" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v>1003.2022</v>
-      </c>
       <c r="M149" s="4" t="n">
         <v>145</v>
       </c>
@@ -13213,17 +13125,6 @@
       <c r="F150" s="4" t="n">
         <v>1006</v>
       </c>
-      <c r="J150" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="K150" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v>1002.65165</v>
-      </c>
       <c r="M150" s="4" t="n">
         <v>146</v>
       </c>
@@ -13259,17 +13160,6 @@
       <c r="F151" s="4" t="n">
         <v>1005.5</v>
       </c>
-      <c r="J151" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="K151" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L151" s="4" t="n">
-        <v>1002.1011</v>
-      </c>
       <c r="M151" s="4" t="n">
         <v>147</v>
       </c>
@@ -13305,17 +13195,6 @@
       <c r="F152" s="4" t="n">
         <v>1005</v>
       </c>
-      <c r="J152" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v>1001.55055</v>
-      </c>
       <c r="M152" s="4" t="n">
         <v>148</v>
       </c>
@@ -13351,17 +13230,6 @@
       <c r="F153" s="4" t="n">
         <v>1004.5</v>
       </c>
-      <c r="J153" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v>1001</v>
-      </c>
       <c r="M153" s="4" t="n">
         <v>149</v>
       </c>
@@ -13397,17 +13265,6 @@
       <c r="F154" s="4" t="n">
         <v>1004</v>
       </c>
-      <c r="J154" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="K154" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="L154" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M154" s="4" t="n">
         <v>150</v>
       </c>
@@ -13518,11 +13375,11 @@
       </c>
       <c r="Q157" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R157" s="4" t="n">
-        <v>1006.2011</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="158">
@@ -13542,11 +13399,11 @@
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R158" s="4" t="n">
-        <v>1006.751229837388</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="159">
@@ -13570,7 +13427,7 @@
         </is>
       </c>
       <c r="R159" s="4" t="n">
-        <v>1006.2011</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="160">
@@ -13590,11 +13447,11 @@
       </c>
       <c r="Q160" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R160" s="4" t="n">
-        <v>1006.75165</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="161">
@@ -13614,11 +13471,11 @@
       </c>
       <c r="Q161" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R161" s="4" t="n">
-        <v>1007.301739252713</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="162">
@@ -13638,11 +13495,11 @@
       </c>
       <c r="Q162" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R162" s="4" t="n">
-        <v>1007.852267708094</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="163">
@@ -13662,11 +13519,11 @@
       </c>
       <c r="Q163" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R163" s="4" t="n">
-        <v>1007.301739252713</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="164">
@@ -13690,7 +13547,7 @@
         </is>
       </c>
       <c r="R164" s="4" t="n">
-        <v>1006.751229837388</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="165">
@@ -13710,11 +13567,11 @@
       </c>
       <c r="Q165" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R165" s="4" t="n">
-        <v>1006.2011</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="166">
@@ -13738,7 +13595,7 @@
         </is>
       </c>
       <c r="R166" s="4" t="n">
-        <v>1005.651229837388</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="167">
@@ -13758,11 +13615,11 @@
       </c>
       <c r="Q167" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R167" s="4" t="n">
-        <v>1005.100777817459</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="168">
@@ -13786,7 +13643,7 @@
         </is>
       </c>
       <c r="R168" s="4" t="n">
-        <v>1004.55055</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="169">
@@ -13806,11 +13663,11 @@
       </c>
       <c r="Q169" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R169" s="4" t="n">
-        <v>1004</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="170">
@@ -13830,11 +13687,11 @@
       </c>
       <c r="Q170" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R170" s="4" t="n">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="171">
@@ -13854,11 +13711,11 @@
       </c>
       <c r="Q171" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R171" s="4" t="n">
-        <v>1002</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="172">
@@ -13878,11 +13735,11 @@
       </c>
       <c r="Q172" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R172" s="4" t="n">
-        <v>1002.100777817459</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="173">
@@ -13906,7 +13763,7 @@
         </is>
       </c>
       <c r="R173" s="4" t="n">
-        <v>1001.55055</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="174">
@@ -13926,11 +13783,11 @@
       </c>
       <c r="Q174" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R174" s="4" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="175">
@@ -13950,11 +13807,11 @@
       </c>
       <c r="Q175" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R175" s="4" t="n">
-        <v>0</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="176">
@@ -13969,6 +13826,17 @@
       <c r="O176" s="4" t="n">
         <v>1007</v>
       </c>
+      <c r="P176" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q176" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R176" s="4" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="177">
       <c r="M177" s="4" t="n">
@@ -13982,6 +13850,17 @@
       <c r="O177" s="4" t="n">
         <v>1006.5</v>
       </c>
+      <c r="P177" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q177" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R177" s="4" t="n">
+        <v>1003.5</v>
+      </c>
     </row>
     <row r="178">
       <c r="M178" s="4" t="n">
@@ -13995,6 +13874,17 @@
       <c r="O178" s="4" t="n">
         <v>1006</v>
       </c>
+      <c r="P178" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q178" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R178" s="4" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="179">
       <c r="M179" s="4" t="n">
@@ -14008,6 +13898,17 @@
       <c r="O179" s="4" t="n">
         <v>1005.5</v>
       </c>
+      <c r="P179" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q179" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R179" s="4" t="n">
+        <v>1004.5</v>
+      </c>
     </row>
     <row r="180">
       <c r="M180" s="4" t="n">
@@ -14021,6 +13922,17 @@
       <c r="O180" s="4" t="n">
         <v>1005</v>
       </c>
+      <c r="P180" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q180" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R180" s="4" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="181">
       <c r="M181" s="4" t="n">
@@ -14034,6 +13946,17 @@
       <c r="O181" s="4" t="n">
         <v>1004.5</v>
       </c>
+      <c r="P181" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q181" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R181" s="4" t="n">
+        <v>1004.5</v>
+      </c>
     </row>
     <row r="182">
       <c r="M182" s="4" t="n">
@@ -14047,6 +13970,17 @@
       <c r="O182" s="4" t="n">
         <v>1005</v>
       </c>
+      <c r="P182" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q182" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R182" s="4" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="183">
       <c r="M183" s="4" t="n">
@@ -14060,6 +13994,17 @@
       <c r="O183" s="4" t="n">
         <v>1005.5</v>
       </c>
+      <c r="P183" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q183" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R183" s="4" t="n">
+        <v>1004.5</v>
+      </c>
     </row>
     <row r="184">
       <c r="M184" s="4" t="n">
@@ -14073,6 +14018,17 @@
       <c r="O184" s="4" t="n">
         <v>1005</v>
       </c>
+      <c r="P184" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q184" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R184" s="4" t="n">
+        <v>12004</v>
+      </c>
     </row>
     <row r="185">
       <c r="M185" s="4" t="n">
@@ -14086,6 +14042,17 @@
       <c r="O185" s="4" t="n">
         <v>1005.5</v>
       </c>
+      <c r="P185" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q185" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R185" s="4" t="n">
+        <v>12004.5005</v>
+      </c>
     </row>
     <row r="186">
       <c r="M186" s="4" t="n">
@@ -14099,6 +14066,17 @@
       <c r="O186" s="4" t="n">
         <v>1006</v>
       </c>
+      <c r="P186" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q186" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R186" s="4" t="n">
+        <v>12005.001</v>
+      </c>
     </row>
     <row r="187">
       <c r="M187" s="4" t="n">
@@ -14112,6 +14090,17 @@
       <c r="O187" s="4" t="n">
         <v>1006.5</v>
       </c>
+      <c r="P187" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q187" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R187" s="4" t="n">
+        <v>12005.5015</v>
+      </c>
     </row>
     <row r="188">
       <c r="M188" s="4" t="n">
@@ -14125,6 +14114,17 @@
       <c r="O188" s="4" t="n">
         <v>1007</v>
       </c>
+      <c r="P188" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q188" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R188" s="4" t="n">
+        <v>12005.001</v>
+      </c>
     </row>
     <row r="189">
       <c r="M189" s="4" t="n">
@@ -14138,6 +14138,17 @@
       <c r="O189" s="4" t="n">
         <v>1006.5</v>
       </c>
+      <c r="P189" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q189" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R189" s="4" t="n">
+        <v>12005.5015</v>
+      </c>
     </row>
     <row r="190">
       <c r="M190" s="4" t="n">
@@ -14151,6 +14162,17 @@
       <c r="O190" s="4" t="n">
         <v>1006</v>
       </c>
+      <c r="P190" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q190" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R190" s="4" t="n">
+        <v>12006.00158113883</v>
+      </c>
     </row>
     <row r="191">
       <c r="M191" s="4" t="n">
@@ -14164,6 +14186,17 @@
       <c r="O191" s="4" t="n">
         <v>1005.5</v>
       </c>
+      <c r="P191" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q191" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R191" s="4" t="n">
+        <v>12005.5015</v>
+      </c>
     </row>
     <row r="192">
       <c r="M192" s="4" t="n">
@@ -14177,6 +14210,17 @@
       <c r="O192" s="4" t="n">
         <v>2006.2011</v>
       </c>
+      <c r="P192" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q192" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R192" s="4" t="n">
+        <v>12006.00158113883</v>
+      </c>
     </row>
     <row r="193">
       <c r="M193" s="4" t="n">
@@ -14190,6 +14234,17 @@
       <c r="O193" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P193" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q193" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R193" s="4" t="n">
+        <v>12006.50180277564</v>
+      </c>
     </row>
     <row r="194">
       <c r="M194" s="4" t="n">
@@ -14203,6 +14258,17 @@
       <c r="O194" s="4" t="n">
         <v>2005.100777817459</v>
       </c>
+      <c r="P194" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q194" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R194" s="4" t="n">
+        <v>13005</v>
+      </c>
     </row>
     <row r="195">
       <c r="M195" s="4" t="n">
@@ -14216,6 +14282,17 @@
       <c r="O195" s="4" t="n">
         <v>2004.55055</v>
       </c>
+      <c r="P195" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q195" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R195" s="4" t="n">
+        <v>13004</v>
+      </c>
     </row>
     <row r="196">
       <c r="M196" s="4" t="n">
@@ -14229,6 +14306,17 @@
       <c r="O196" s="4" t="n">
         <v>2004</v>
       </c>
+      <c r="P196" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q196" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R196" s="4" t="n">
+        <v>13003</v>
+      </c>
     </row>
     <row r="197">
       <c r="M197" s="4" t="n">
@@ -14242,6 +14330,17 @@
       <c r="O197" s="4" t="n">
         <v>2004.55055</v>
       </c>
+      <c r="P197" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q197" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R197" s="4" t="n">
+        <v>12004.7519830532</v>
+      </c>
     </row>
     <row r="198">
       <c r="M198" s="4" t="n">
@@ -14255,6 +14354,17 @@
       <c r="O198" s="4" t="n">
         <v>2005.100777817459</v>
       </c>
+      <c r="P198" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q198" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R198" s="4" t="n">
+        <v>12004.20155563492</v>
+      </c>
     </row>
     <row r="199">
       <c r="M199" s="4" t="n">
@@ -14268,6 +14378,17 @@
       <c r="O199" s="4" t="n">
         <v>2004.55055</v>
       </c>
+      <c r="P199" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q199" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R199" s="4" t="n">
+        <v>12003.65122983739</v>
+      </c>
     </row>
     <row r="200">
       <c r="M200" s="4" t="n">
@@ -14281,6 +14402,17 @@
       <c r="O200" s="4" t="n">
         <v>2005.100777817459</v>
       </c>
+      <c r="P200" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q200" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R200" s="4" t="n">
+        <v>12003.10077781746</v>
+      </c>
     </row>
     <row r="201">
       <c r="M201" s="4" t="n">
@@ -14294,6 +14426,17 @@
       <c r="O201" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P201" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q201" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R201" s="4" t="n">
+        <v>12002.55055</v>
+      </c>
     </row>
     <row r="202">
       <c r="M202" s="4" t="n">
@@ -14307,6 +14450,17 @@
       <c r="O202" s="4" t="n">
         <v>2005.1011</v>
       </c>
+      <c r="P202" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q202" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R202" s="4" t="n">
+        <v>12002</v>
+      </c>
     </row>
     <row r="203">
       <c r="M203" s="4" t="n">
@@ -14320,6 +14474,17 @@
       <c r="O203" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P203" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q203" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R203" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="204">
       <c r="M204" s="4" t="n">
@@ -14333,6 +14498,17 @@
       <c r="O204" s="4" t="n">
         <v>2006.201555634919</v>
       </c>
+      <c r="P204" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q204" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R204" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="205">
       <c r="M205" s="4" t="n">
@@ -14346,6 +14522,17 @@
       <c r="O205" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P205" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q205" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R205" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="206">
       <c r="M206" s="4" t="n">
@@ -14359,6 +14546,17 @@
       <c r="O206" s="4" t="n">
         <v>2005.1011</v>
       </c>
+      <c r="P206" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q206" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R206" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="207">
       <c r="M207" s="4" t="n">
@@ -14372,6 +14570,17 @@
       <c r="O207" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P207" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q207" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R207" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="208">
       <c r="M208" s="4" t="n">
@@ -14385,6 +14594,17 @@
       <c r="O208" s="4" t="n">
         <v>2005.100777817459</v>
       </c>
+      <c r="P208" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q208" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R208" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="209">
       <c r="M209" s="4" t="n">
@@ -14398,6 +14618,17 @@
       <c r="O209" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
+      <c r="P209" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q209" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R209" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="210">
       <c r="M210" s="4" t="n">
@@ -14411,6 +14642,17 @@
       <c r="O210" s="4" t="n">
         <v>2006.201555634919</v>
       </c>
+      <c r="P210" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q210" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R210" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="211">
       <c r="M211" s="4" t="n">
@@ -14424,6 +14666,17 @@
       <c r="O211" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
+      <c r="P211" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q211" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R211" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="212">
       <c r="M212" s="4" t="n">
@@ -14437,6 +14690,17 @@
       <c r="O212" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
+      <c r="P212" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q212" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R212" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="213">
       <c r="M213" s="4" t="n">
@@ -14450,6 +14714,17 @@
       <c r="O213" s="4" t="n">
         <v>2005.65165</v>
       </c>
+      <c r="P213" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q213" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R213" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="214">
       <c r="M214" s="4" t="n">
@@ -14463,6 +14738,17 @@
       <c r="O214" s="4" t="n">
         <v>2006.2022</v>
       </c>
+      <c r="P214" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q214" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R214" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="215">
       <c r="M215" s="4" t="n">
@@ -14476,6 +14762,17 @@
       <c r="O215" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
+      <c r="P215" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q215" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R215" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="216">
       <c r="M216" s="4" t="n">
@@ -14489,6 +14786,17 @@
       <c r="O216" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
+      <c r="P216" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q216" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R216" s="4" t="n">
+        <v>12004.2011</v>
+      </c>
     </row>
     <row r="217">
       <c r="M217" s="4" t="n">
@@ -14502,6 +14810,17 @@
       <c r="O217" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
+      <c r="P217" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q217" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R217" s="4" t="n">
+        <v>12003.65122983739</v>
+      </c>
     </row>
     <row r="218">
       <c r="M218" s="4" t="n">
@@ -14515,6 +14834,17 @@
       <c r="O218" s="4" t="n">
         <v>2007.302333452378</v>
       </c>
+      <c r="P218" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="Q218" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R218" s="4" t="n">
+        <v>12003.10077781746</v>
+      </c>
     </row>
     <row r="219">
       <c r="M219" s="4" t="n">
@@ -14528,6 +14858,17 @@
       <c r="O219" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
+      <c r="P219" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q219" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R219" s="4" t="n">
+        <v>12002.55055</v>
+      </c>
     </row>
     <row r="220">
       <c r="M220" s="4" t="n">
@@ -14541,6 +14882,17 @@
       <c r="O220" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
+      <c r="P220" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="Q220" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R220" s="4" t="n">
+        <v>12002</v>
+      </c>
     </row>
     <row r="221">
       <c r="M221" s="4" t="n">
@@ -14554,6 +14906,17 @@
       <c r="O221" s="4" t="n">
         <v>2005.65165</v>
       </c>
+      <c r="P221" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q221" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R221" s="4" t="n">
+        <v>11003.50180277564</v>
+      </c>
     </row>
     <row r="222">
       <c r="M222" s="4" t="n">
@@ -14567,6 +14930,17 @@
       <c r="O222" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
+      <c r="P222" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q222" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R222" s="4" t="n">
+        <v>11003.00158113883</v>
+      </c>
     </row>
     <row r="223">
       <c r="M223" s="4" t="n">
@@ -14580,6 +14954,17 @@
       <c r="O223" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
+      <c r="P223" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q223" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R223" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="224">
       <c r="M224" s="4" t="n">
@@ -14593,6 +14978,17 @@
       <c r="O224" s="4" t="n">
         <v>2006.2022</v>
       </c>
+      <c r="P224" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q224" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R224" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="225">
       <c r="M225" s="4" t="n">
@@ -14606,6 +15002,17 @@
       <c r="O225" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
+      <c r="P225" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q225" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R225" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="226">
       <c r="M226" s="4" t="n">
@@ -14619,6 +15026,17 @@
       <c r="O226" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
+      <c r="P226" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q226" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R226" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="227">
       <c r="M227" s="4" t="n">
@@ -14632,6 +15050,17 @@
       <c r="O227" s="4" t="n">
         <v>2007.85275</v>
       </c>
+      <c r="P227" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q227" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R227" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="228">
       <c r="M228" s="4" t="n">
@@ -14645,6 +15074,17 @@
       <c r="O228" s="4" t="n">
         <v>2008.403111269837</v>
       </c>
+      <c r="P228" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q228" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R228" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="229">
       <c r="M229" s="4" t="n">
@@ -14658,6 +15098,17 @@
       <c r="O229" s="4" t="n">
         <v>2007.85275</v>
       </c>
+      <c r="P229" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q229" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R229" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="230">
       <c r="M230" s="4" t="n">
@@ -14671,6 +15122,17 @@
       <c r="O230" s="4" t="n">
         <v>2008.403207023542</v>
       </c>
+      <c r="P230" s="4" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q230" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R230" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="231">
       <c r="M231" s="4" t="n">
@@ -14684,6 +15146,17 @@
       <c r="O231" s="4" t="n">
         <v>2007.852961840644</v>
       </c>
+      <c r="P231" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q231" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R231" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="232">
       <c r="M232" s="4" t="n">
@@ -14697,6 +15170,17 @@
       <c r="O232" s="4" t="n">
         <v>2007.302804460732</v>
       </c>
+      <c r="P232" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q232" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R232" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="233">
       <c r="M233" s="4" t="n">
@@ -14710,6 +15194,17 @@
       <c r="O233" s="4" t="n">
         <v>2006.75275</v>
       </c>
+      <c r="P233" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q233" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R233" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="234">
       <c r="M234" s="4" t="n">
@@ -14723,6 +15218,17 @@
       <c r="O234" s="4" t="n">
         <v>2007.3033</v>
       </c>
+      <c r="P234" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q234" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R234" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="235">
       <c r="M235" s="4" t="n">
@@ -14736,6 +15242,17 @@
       <c r="O235" s="4" t="n">
         <v>2007.853345519392</v>
       </c>
+      <c r="P235" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q235" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R235" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="236">
       <c r="M236" s="4" t="n">
@@ -14749,6 +15266,17 @@
       <c r="O236" s="4" t="n">
         <v>2008.403478505426</v>
       </c>
+      <c r="P236" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q236" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R236" s="4" t="n">
+        <v>11002.001</v>
+      </c>
     </row>
     <row r="237">
       <c r="M237" s="4" t="n">
@@ -14762,6 +15290,17 @@
       <c r="O237" s="4" t="n">
         <v>2007.852961840644</v>
       </c>
+      <c r="P237" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q237" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R237" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="238">
       <c r="M238" s="4" t="n">
@@ -14775,6 +15314,17 @@
       <c r="O238" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
+      <c r="P238" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q238" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R238" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="239">
       <c r="M239" s="4" t="n">
@@ -14788,6 +15338,17 @@
       <c r="O239" s="4" t="n">
         <v>2007.85275</v>
       </c>
+      <c r="P239" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q239" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R239" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="240">
       <c r="M240" s="4" t="n">
@@ -14801,6 +15362,17 @@
       <c r="O240" s="4" t="n">
         <v>2007.302333452378</v>
       </c>
+      <c r="P240" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q240" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R240" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="241">
       <c r="M241" s="4" t="n">
@@ -14814,6 +15386,17 @@
       <c r="O241" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
+      <c r="P241" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q241" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R241" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="242">
       <c r="M242" s="4" t="n">
@@ -14827,6 +15410,17 @@
       <c r="O242" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
+      <c r="P242" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q242" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R242" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="243">
       <c r="M243" s="4" t="n">
@@ -14840,6 +15434,17 @@
       <c r="O243" s="4" t="n">
         <v>2006.75165</v>
       </c>
+      <c r="P243" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q243" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R243" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="244">
       <c r="M244" s="4" t="n">
@@ -14853,6 +15458,17 @@
       <c r="O244" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
+      <c r="P244" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q244" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R244" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="245">
       <c r="M245" s="4" t="n">
@@ -14866,6 +15482,17 @@
       <c r="O245" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
+      <c r="P245" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q245" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R245" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="246">
       <c r="M246" s="4" t="n">
@@ -14879,6 +15506,17 @@
       <c r="O246" s="4" t="n">
         <v>2007.3022</v>
       </c>
+      <c r="P246" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q246" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R246" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="247">
       <c r="M247" s="4" t="n">
@@ -14892,6 +15530,17 @@
       <c r="O247" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
+      <c r="P247" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q247" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R247" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="248">
       <c r="M248" s="4" t="n">
@@ -14905,6 +15554,17 @@
       <c r="O248" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
+      <c r="P248" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q248" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R248" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="249">
       <c r="M249" s="4" t="n">
@@ -14918,6 +15578,17 @@
       <c r="O249" s="4" t="n">
         <v>2007.85275</v>
       </c>
+      <c r="P249" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q249" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R249" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
     </row>
     <row r="250">
       <c r="M250" s="4" t="n">
@@ -14931,6 +15602,17 @@
       <c r="O250" s="4" t="n">
         <v>2008.403111269837</v>
       </c>
+      <c r="P250" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q250" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R250" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="251">
       <c r="M251" s="4" t="n">
@@ -14944,6 +15626,17 @@
       <c r="O251" s="4" t="n">
         <v>2007.2011</v>
       </c>
+      <c r="P251" s="4" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q251" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R251" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="252">
       <c r="M252" s="4" t="n">
@@ -14957,6 +15650,17 @@
       <c r="O252" s="4" t="n">
         <v>2006.651229837388</v>
       </c>
+      <c r="P252" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q252" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R252" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="253">
       <c r="M253" s="4" t="n">
@@ -14970,6 +15674,17 @@
       <c r="O253" s="4" t="n">
         <v>2006.100777817459</v>
       </c>
+      <c r="P253" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q253" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R253" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="254">
       <c r="M254" s="4" t="n">
@@ -14983,6 +15698,17 @@
       <c r="O254" s="4" t="n">
         <v>2005.55055</v>
       </c>
+      <c r="P254" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q254" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R254" s="4" t="n">
+        <v>11002.001</v>
+      </c>
     </row>
     <row r="255">
       <c r="M255" s="4" t="n">
@@ -14996,6 +15722,17 @@
       <c r="O255" s="4" t="n">
         <v>2005</v>
       </c>
+      <c r="P255" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q255" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R255" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="256">
       <c r="M256" s="4" t="n">
@@ -15009,6 +15746,17 @@
       <c r="O256" s="4" t="n">
         <v>2005.55055</v>
       </c>
+      <c r="P256" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q256" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R256" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="257">
       <c r="M257" s="4" t="n">
@@ -15022,6 +15770,17 @@
       <c r="O257" s="4" t="n">
         <v>2005</v>
       </c>
+      <c r="P257" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q257" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R257" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="258">
       <c r="M258" s="4" t="n">
@@ -15035,6 +15794,17 @@
       <c r="O258" s="4" t="n">
         <v>2004</v>
       </c>
+      <c r="P258" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q258" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R258" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="259">
       <c r="M259" s="4" t="n">
@@ -15048,6 +15818,17 @@
       <c r="O259" s="4" t="n">
         <v>2003</v>
       </c>
+      <c r="P259" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q259" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R259" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="260">
       <c r="M260" s="4" t="n">
@@ -15061,6 +15842,17 @@
       <c r="O260" s="4" t="n">
         <v>2003.100777817459</v>
       </c>
+      <c r="P260" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q260" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R260" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="261">
       <c r="M261" s="4" t="n">
@@ -15074,6 +15866,17 @@
       <c r="O261" s="4" t="n">
         <v>2002.55055</v>
       </c>
+      <c r="P261" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q261" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R261" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="262">
       <c r="M262" s="4" t="n">
@@ -15087,6 +15890,17 @@
       <c r="O262" s="4" t="n">
         <v>2002</v>
       </c>
+      <c r="P262" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q262" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R262" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="263">
       <c r="M263" s="4" t="n">
@@ -15100,6 +15914,17 @@
       <c r="O263" s="4" t="n">
         <v>1008.155070749452</v>
       </c>
+      <c r="P263" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q263" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R263" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="264">
       <c r="M264" s="4" t="n">
@@ -15113,6 +15938,17 @@
       <c r="O264" s="4" t="n">
         <v>1007.604666904756</v>
       </c>
+      <c r="P264" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q264" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R264" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="265">
       <c r="M265" s="4" t="n">
@@ -15126,6 +15962,17 @@
       <c r="O265" s="4" t="n">
         <v>1007.054295637322</v>
       </c>
+      <c r="P265" s="4" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q265" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R265" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="266">
       <c r="M266" s="4" t="n">
@@ -15139,6 +15986,17 @@
       <c r="O266" s="4" t="n">
         <v>1006.503889087297</v>
       </c>
+      <c r="P266" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q266" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R266" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="267">
       <c r="M267" s="4" t="n">
@@ -15152,6 +16010,17 @@
       <c r="O267" s="4" t="n">
         <v>1005.953521718331</v>
       </c>
+      <c r="P267" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q267" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R267" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="268">
       <c r="M268" s="4" t="n">
@@ -15165,6 +16034,17 @@
       <c r="O268" s="4" t="n">
         <v>1005.403111269837</v>
       </c>
+      <c r="P268" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q268" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R268" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="269">
       <c r="M269" s="4" t="n">
@@ -15178,6 +16058,17 @@
       <c r="O269" s="4" t="n">
         <v>1004.85275</v>
       </c>
+      <c r="P269" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q269" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R269" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="270">
       <c r="M270" s="4" t="n">
@@ -15191,6 +16082,17 @@
       <c r="O270" s="4" t="n">
         <v>1004.302333452378</v>
       </c>
+      <c r="P270" s="4" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q270" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R270" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="271">
       <c r="M271" s="4" t="n">
@@ -15204,6 +16106,17 @@
       <c r="O271" s="4" t="n">
         <v>1003.751983053202</v>
       </c>
+      <c r="P271" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="Q271" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R271" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="272">
       <c r="M272" s="4" t="n">
@@ -15217,6 +16130,17 @@
       <c r="O272" s="4" t="n">
         <v>1003.201555634919</v>
       </c>
+      <c r="P272" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q272" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R272" s="4" t="n">
+        <v>11001</v>
+      </c>
     </row>
     <row r="273">
       <c r="M273" s="4" t="n">
@@ -15230,6 +16154,17 @@
       <c r="O273" s="4" t="n">
         <v>1002.651229837388</v>
       </c>
+      <c r="P273" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q273" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R273" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="274">
       <c r="M274" s="4" t="n">
@@ -15243,6 +16178,17 @@
       <c r="O274" s="4" t="n">
         <v>1002.100777817459</v>
       </c>
+      <c r="P274" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q274" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R274" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="275">
       <c r="M275" s="4" t="n">
@@ -15256,6 +16202,17 @@
       <c r="O275" s="4" t="n">
         <v>1001.55055</v>
       </c>
+      <c r="P275" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q275" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R275" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
     </row>
     <row r="276">
       <c r="M276" s="4" t="n">
@@ -15269,6 +16226,17 @@
       <c r="O276" s="4" t="n">
         <v>1001</v>
       </c>
+      <c r="P276" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q276" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R276" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
     </row>
     <row r="277">
       <c r="M277" s="4" t="n">
@@ -15282,57 +16250,2071 @@
       <c r="O277" s="4" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="278"/>
-    <row r="279"/>
+      <c r="P277" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q277" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R277" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="P278" s="4" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q278" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R278" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="P279" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q279" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R279" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
     <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 143 bước (296.97 ms).</t>
-        </is>
-      </c>
-      <c r="D280" s="6" t="inlineStr">
+      <c r="P280" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q280" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R280" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="P281" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q281" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R281" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="P282" s="4" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q282" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R282" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="P283" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q283" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R283" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="P284" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q284" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R284" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="P285" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q285" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R285" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="P286" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q286" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R286" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="P287" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q287" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R287" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="P288" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q288" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R288" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="P289" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q289" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R289" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="P290" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q290" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R290" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="P291" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q291" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R291" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="P292" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q292" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R292" s="4" t="n">
+        <v>11003.00141421356</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="P293" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q293" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R293" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="P294" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q294" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R294" s="4" t="n">
+        <v>11003.00158113883</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="P295" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q295" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R295" s="4" t="n">
+        <v>11002.5015</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="P296" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q296" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R296" s="4" t="n">
+        <v>11003.00158113883</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="P297" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q297" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R297" s="4" t="n">
+        <v>11003.50180277564</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="P298" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q298" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R298" s="4" t="n">
+        <v>11004.00223606798</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="P299" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q299" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R299" s="4" t="n">
+        <v>11003.50206155281</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="P300" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q300" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R300" s="4" t="n">
+        <v>11004.00223606798</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="P301" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q301" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R301" s="4" t="n">
+        <v>11003.50206155281</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="P302" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q302" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R302" s="4" t="n">
+        <v>11003.002</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="P303" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q303" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R303" s="4" t="n">
+        <v>11002.5015</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="P304" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q304" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R304" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="P305" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q305" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R305" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="P306" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q306" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R306" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="P307" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q307" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R307" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="P308" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q308" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R308" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="P309" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q309" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R309" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="P310" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="Q310" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R310" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="P311" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q311" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R311" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="P312" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q312" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R312" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="P313" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q313" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R313" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="P314" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q314" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R314" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="P315" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q315" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R315" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="P316" s="4" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q316" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R316" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="P317" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="Q317" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R317" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="P318" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q318" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R318" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="P319" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q319" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R319" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="P320" s="4" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q320" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R320" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="P321" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q321" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R321" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="P322" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q322" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R322" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="P323" s="4" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q323" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R323" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="P324" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q324" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R324" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="P325" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q325" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R325" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="P326" s="4" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q326" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R326" s="4" t="n">
+        <v>12004.2011</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="P327" s="4" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q327" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R327" s="4" t="n">
+        <v>12005.2011</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="P328" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q328" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R328" s="4" t="n">
+        <v>12004.65122983739</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="P329" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q329" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R329" s="4" t="n">
+        <v>12004.10077781746</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="P330" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="Q330" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R330" s="4" t="n">
+        <v>12003.55055</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="P331" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q331" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R331" s="4" t="n">
+        <v>12003</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="P332" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q332" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R332" s="4" t="n">
+        <v>12002</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="P333" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q333" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R333" s="4" t="n">
+        <v>11003.50180277564</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="P334" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q334" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R334" s="4" t="n">
+        <v>11003.00158113883</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="P335" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q335" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R335" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="P336" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q336" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R336" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="P337" s="4" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q337" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R337" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="P338" s="4" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q338" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R338" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="P339" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q339" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R339" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="P340" s="4" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q340" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R340" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="P341" s="4" t="n">
+        <v>337</v>
+      </c>
+      <c r="Q341" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R341" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="P342" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q342" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R342" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="P343" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q343" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R343" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="P344" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q344" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R344" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="P345" s="4" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q345" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R345" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="P346" s="4" t="n">
+        <v>342</v>
+      </c>
+      <c r="Q346" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R346" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="P347" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q347" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R347" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="P348" s="4" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q348" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R348" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="P349" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="Q349" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R349" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="P350" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="Q350" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R350" s="4" t="n">
+        <v>11003.00141421356</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="P351" s="4" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q351" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R351" s="4" t="n">
+        <v>11003.50180277564</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="P352" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q352" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R352" s="4" t="n">
+        <v>11003.00158113883</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="P353" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q353" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R353" s="4" t="n">
+        <v>11003.50180277564</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="P354" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q354" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R354" s="4" t="n">
+        <v>11003.00141421356</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="P355" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q355" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R355" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="P356" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q356" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R356" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="P357" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q357" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R357" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="P358" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q358" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R358" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="P359" s="4" t="n">
+        <v>355</v>
+      </c>
+      <c r="Q359" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R359" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="P360" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q360" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R360" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="P361" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q361" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R361" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="P362" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q362" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R362" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="P363" s="4" t="n">
+        <v>359</v>
+      </c>
+      <c r="Q363" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R363" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="P364" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q364" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R364" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="P365" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q365" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R365" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="P366" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q366" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R366" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="P367" s="4" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q367" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R367" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="P368" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q368" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R368" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="P369" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q369" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R369" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="P370" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q370" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R370" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="P371" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q371" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R371" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="P372" s="4" t="n">
+        <v>368</v>
+      </c>
+      <c r="Q372" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R372" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="P373" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q373" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R373" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="P374" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q374" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R374" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="P375" s="4" t="n">
+        <v>371</v>
+      </c>
+      <c r="Q375" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R375" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="P376" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="Q376" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R376" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="P377" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q377" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R377" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="P378" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q378" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R378" s="4" t="n">
+        <v>11003.00141421356</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="P379" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q379" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R379" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="P380" s="4" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q380" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R380" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="P381" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q381" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R381" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="P382" s="4" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q382" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R382" s="4" t="n">
+        <v>11002.00070710678</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="P383" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q383" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R383" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="P384" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q384" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R384" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="P385" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="Q385" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R385" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="P386" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q386" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R386" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="P387" s="4" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q387" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R387" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="P388" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q388" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R388" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="P389" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="Q389" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R389" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="P390" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="Q390" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R390" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="P391" s="4" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q391" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R391" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="P392" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q392" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R392" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="P393" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q393" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R393" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="P394" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q394" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R394" s="4" t="n">
+        <v>11003.001</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="P395" s="4" t="n">
+        <v>391</v>
+      </c>
+      <c r="Q395" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R395" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="P396" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q396" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R396" s="4" t="n">
+        <v>11003.001</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="P397" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q397" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R397" s="4" t="n">
+        <v>11002.50111803399</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="P398" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="Q398" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R398" s="4" t="n">
+        <v>11002.001</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="P399" s="4" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q399" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R399" s="4" t="n">
+        <v>11001.5005</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="P400" s="4" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q400" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R400" s="4" t="n">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="P401" s="4" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q401" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R401" s="4" t="n">
+        <v>11004.2011</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="P402" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="Q402" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R402" s="4" t="n">
+        <v>11007.40077781746</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="P403" s="4" t="n">
+        <v>399</v>
+      </c>
+      <c r="Q403" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R403" s="4" t="n">
+        <v>11007.95122983739</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="P404" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q404" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R404" s="4" t="n">
+        <v>11007.4011</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="P405" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q405" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R405" s="4" t="n">
+        <v>11008.4011</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="P406" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="Q406" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R406" s="4" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="P407" s="4" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q407" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R407" s="4" t="n">
+        <v>11005.5005</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="P408" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="Q408" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R408" s="4" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="P409" s="4" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q409" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R409" s="4" t="n">
+        <v>11005.5005</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="P410" s="4" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q410" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R410" s="4" t="n">
+        <v>11006.00070710678</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="P411" s="4" t="n">
+        <v>407</v>
+      </c>
+      <c r="Q411" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R411" s="4" t="n">
+        <v>11005.5005</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="P412" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="Q412" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R412" s="4" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="P413" s="4" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R413" s="4" t="n">
+        <v>11005.5005</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="P414" s="4" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q414" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R414" s="4" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="P415" s="4" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="n">
+        <v>11006</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="P416" s="4" t="n">
+        <v>412</v>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R416" s="4" t="n">
+        <v>11006.55055</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="P417" s="4" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q417" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R417" s="4" t="n">
+        <v>11007.1011</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="P418" s="4" t="n">
+        <v>414</v>
+      </c>
+      <c r="Q418" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R418" s="4" t="n">
+        <v>22008.65165</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="P419" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="Q419" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R419" s="4" t="n">
+        <v>22008.65122983739</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="P420" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q420" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R420" s="4" t="n">
+        <v>22008.10077781746</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="P421" s="4" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q421" s="4" t="inlineStr">
+        <is>
+          <t>XUỐNG</t>
+        </is>
+      </c>
+      <c r="R421" s="4" t="n">
+        <v>22007.55055</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="P422" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q422" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R422" s="4" t="n">
+        <v>22007</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="P423" s="4" t="n">
+        <v>419</v>
+      </c>
+      <c r="Q423" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R423" s="4" t="n">
+        <v>11009.3022</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="P424" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q424" s="4" t="inlineStr">
+        <is>
+          <t>TRÁI</t>
+        </is>
+      </c>
+      <c r="R424" s="4" t="n">
+        <v>11008.75226770809</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="P425" s="4" t="n">
+        <v>421</v>
+      </c>
+      <c r="Q425" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R425" s="4" t="n">
+        <v>11008.20173925271</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="P426" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q426" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R426" s="4" t="n">
+        <v>11007.65122983739</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="P427" s="4" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q427" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R427" s="4" t="n">
+        <v>11007.10077781746</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="P428" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q428" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R428" s="4" t="n">
+        <v>11006.55055</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="P429" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q429" s="4" t="inlineStr">
+        <is>
+          <t>PHẢI</t>
+        </is>
+      </c>
+      <c r="R429" s="4" t="n">
+        <v>11006</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="P430" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q430" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R430" s="4" t="n">
+        <v>11005</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="P431" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q431" s="4" t="inlineStr">
+        <is>
+          <t>LÊN</t>
+        </is>
+      </c>
+      <c r="R431" s="4" t="n">
+        <v>11004</v>
+      </c>
+    </row>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 143 bước (294.98 ms).</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="inlineStr">
         <is>
           <t>✗ Thất bại: Bị kẹt tại đỉnh cục bộ 
 (H = 1003.0).</t>
         </is>
       </c>
-      <c r="G280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 139 bước (428.06 ms).</t>
-        </is>
-      </c>
-      <c r="J280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 150 bước (275.15 ms).</t>
-        </is>
-      </c>
-      <c r="M280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 273 bước (696.95 ms).</t>
-        </is>
-      </c>
-      <c r="P280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 171 bước (460.89 ms).</t>
-        </is>
-      </c>
-      <c r="S280" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 143 bước (277.57 ms).</t>
-        </is>
-      </c>
-    </row>
-    <row r="281"/>
+      <c r="G434" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 137 bước (394.58 ms).</t>
+        </is>
+      </c>
+      <c r="J434" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 139 bước (261.58 ms).</t>
+        </is>
+      </c>
+      <c r="M434" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 273 bước (705.63 ms).</t>
+        </is>
+      </c>
+      <c r="P434" s="6" t="inlineStr">
+        <is>
+          <t>✗ Thất bại: Bị kẹt tại đỉnh cục bộ 
+(H = 11004.0).</t>
+        </is>
+      </c>
+      <c r="S434" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 143 bước (280.47 ms).</t>
+        </is>
+      </c>
+    </row>
+    <row r="435"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="D280:F281"/>
-    <mergeCell ref="A280:C281"/>
-    <mergeCell ref="G280:I281"/>
-    <mergeCell ref="P280:R281"/>
-    <mergeCell ref="J280:L281"/>
-    <mergeCell ref="S280:U281"/>
-    <mergeCell ref="M280:O281"/>
+    <mergeCell ref="G434:I435"/>
+    <mergeCell ref="J434:L435"/>
+    <mergeCell ref="M434:O435"/>
+    <mergeCell ref="P434:R435"/>
+    <mergeCell ref="A434:C435"/>
+    <mergeCell ref="D434:F435"/>
+    <mergeCell ref="S434:U435"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15495,7 +18477,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>296.97</v>
+        <v>294.98</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>143</v>
@@ -15535,7 +18517,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>435.18</v>
+        <v>437.49</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>152</v>
@@ -15575,10 +18557,10 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>428.06</v>
+        <v>394.58</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>431028</v>
@@ -15615,10 +18597,10 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>275.15</v>
+        <v>261.58</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>431028</v>
@@ -15655,7 +18637,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>696.95</v>
+        <v>705.63</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>273</v>
@@ -15695,23 +18677,23 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>460.89</v>
+        <v>652.48</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>171</v>
+        <v>427</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>431028</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0</v>
+        <v>11004</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>431028</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>✓ Thành công</t>
+        <v>420024</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>✗ Thất bại (H=11004.0)</t>
         </is>
       </c>
       <c r="H10" s="8" t="n"/>
@@ -15735,7 +18717,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>277.57</v>
+        <v>280.47</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>143</v>
@@ -15949,16 +18931,16 @@
         <v>228924</v>
       </c>
       <c r="L17" s="11" t="n">
+        <v>270046.6</v>
+      </c>
+      <c r="M17" s="11" t="n">
         <v>261842.5</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>228964.8</v>
       </c>
       <c r="N17" s="11" t="n">
         <v>228025.2</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>228536.3</v>
+        <v>218024.2</v>
       </c>
       <c r="P17" s="11" t="n">
         <v>245434.2</v>
@@ -15990,13 +18972,13 @@
         <v>228025.2</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>226800.5</v>
+        <v>228025.2</v>
       </c>
       <c r="N18" s="11" t="n">
         <v>217023.5</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>218229.2</v>
+        <v>216022.3</v>
       </c>
       <c r="P18" s="11" t="n">
         <v>228025.1</v>
@@ -16028,13 +19010,13 @@
         <v>218024.3</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>217840.3</v>
+        <v>218024.3</v>
       </c>
       <c r="N19" s="11" t="n">
         <v>216022.7</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>217023.8</v>
+        <v>214022.8</v>
       </c>
       <c r="P19" s="11" t="n">
         <v>218024.1</v>
@@ -16066,13 +19048,13 @@
         <v>217023.4</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>216778.5</v>
+        <v>217023.4</v>
       </c>
       <c r="N20" s="11" t="n">
         <v>215020.9</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>216024.2</v>
+        <v>213020.8</v>
       </c>
       <c r="P20" s="11" t="n">
         <v>217023.2</v>
@@ -16101,16 +19083,16 @@
         <v>216023.4</v>
       </c>
       <c r="L21" s="11" t="n">
+        <v>216024.8</v>
+      </c>
+      <c r="M21" s="11" t="n">
         <v>216024.7</v>
-      </c>
-      <c r="M21" s="11" t="n">
-        <v>216023.5</v>
       </c>
       <c r="N21" s="11" t="n">
         <v>214021.8</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>216022.3</v>
+        <v>212018.9</v>
       </c>
       <c r="P21" s="11" t="n">
         <v>216024.4</v>
@@ -16139,16 +19121,16 @@
         <v>215409.8</v>
       </c>
       <c r="L22" s="11" t="n">
+        <v>216023.2</v>
+      </c>
+      <c r="M22" s="11" t="n">
         <v>216023.1</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <v>215654.7</v>
       </c>
       <c r="N22" s="11" t="n">
         <v>213591.4</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>215021</v>
+        <v>211017.5</v>
       </c>
       <c r="P22" s="11" t="n">
         <v>216022.8</v>
@@ -16180,13 +19162,13 @@
         <v>216022.1</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>215021</v>
+        <v>216022.1</v>
       </c>
       <c r="N23" s="11" t="n">
         <v>213018.6</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>214592.9</v>
+        <v>210016.7</v>
       </c>
       <c r="P23" s="11" t="n">
         <v>216021.9</v>
@@ -16215,16 +19197,16 @@
         <v>214206.5</v>
       </c>
       <c r="L24" s="11" t="n">
+        <v>215653.9</v>
+      </c>
+      <c r="M24" s="11" t="n">
         <v>215328.3</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>214531.9</v>
       </c>
       <c r="N24" s="11" t="n">
         <v>212018.3</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>214021.8</v>
+        <v>209019.7</v>
       </c>
       <c r="P24" s="11" t="n">
         <v>215021.5</v>
@@ -16253,16 +19235,16 @@
         <v>214021.8</v>
       </c>
       <c r="L25" s="11" t="n">
+        <v>215020.5</v>
+      </c>
+      <c r="M25" s="11" t="n">
         <v>215021.4</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>214022</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>211018.7</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>214019.9</v>
+        <v>209014.9</v>
       </c>
       <c r="P25" s="11" t="n">
         <v>214755.3</v>
@@ -16291,16 +19273,16 @@
         <v>214020.1</v>
       </c>
       <c r="L26" s="11" t="n">
+        <v>214021.8</v>
+      </c>
+      <c r="M26" s="11" t="n">
         <v>214653.5</v>
-      </c>
-      <c r="M26" s="11" t="n">
-        <v>214020.3</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>210304.1</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>213020.8</v>
+        <v>207012.7</v>
       </c>
       <c r="P26" s="11" t="n">
         <v>214021.1</v>
@@ -16329,16 +19311,16 @@
         <v>213021.2</v>
       </c>
       <c r="L27" s="11" t="n">
+        <v>214020.2</v>
+      </c>
+      <c r="M27" s="11" t="n">
         <v>214021.1</v>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>213347.1</v>
       </c>
       <c r="N27" s="11" t="n">
         <v>210016.5</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>213018.9</v>
+        <v>206011.8</v>
       </c>
       <c r="P27" s="11" t="n">
         <v>214019.5</v>
@@ -16367,16 +19349,16 @@
         <v>213019.5</v>
       </c>
       <c r="L28" s="11" t="n">
+        <v>213469.2</v>
+      </c>
+      <c r="M28" s="11" t="n">
         <v>214019.5</v>
-      </c>
-      <c r="M28" s="11" t="n">
-        <v>213019.8</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>209021.2</v>
       </c>
       <c r="O28" s="11" t="n">
-        <v>212019.8</v>
+        <v>5436.9</v>
       </c>
       <c r="P28" s="11" t="n">
         <v>213020.7</v>
@@ -16405,16 +19387,16 @@
         <v>212692.2</v>
       </c>
       <c r="L29" s="11" t="n">
+        <v>213020</v>
+      </c>
+      <c r="M29" s="11" t="n">
         <v>213020.8</v>
-      </c>
-      <c r="M29" s="11" t="n">
-        <v>213018.1</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>209018.2</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>212017.9</v>
+        <v>4007.5</v>
       </c>
       <c r="P29" s="11" t="n">
         <v>213019.1</v>
@@ -16443,16 +19425,16 @@
         <v>212019</v>
       </c>
       <c r="L30" s="11" t="n">
+        <v>213018.5</v>
+      </c>
+      <c r="M30" s="11" t="n">
         <v>213019.3</v>
-      </c>
-      <c r="M30" s="11" t="n">
-        <v>212019.8</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>209015.1</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>211019.4</v>
+        <v>2012.3</v>
       </c>
       <c r="P30" s="11" t="n">
         <v>213018.1</v>
@@ -16481,16 +19463,16 @@
         <v>212017.3</v>
       </c>
       <c r="L31" s="11" t="n">
+        <v>212019.8</v>
+      </c>
+      <c r="M31" s="11" t="n">
         <v>212468.2</v>
-      </c>
-      <c r="M31" s="11" t="n">
-        <v>212018.1</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>208012.3</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>211017.5</v>
+        <v>2007.5</v>
       </c>
       <c r="P31" s="11" t="n">
         <v>212019.3</v>
@@ -16519,16 +19501,16 @@
         <v>211019</v>
       </c>
       <c r="L32" s="11" t="n">
+        <v>212018.2</v>
+      </c>
+      <c r="M32" s="11" t="n">
         <v>212019</v>
-      </c>
-      <c r="M32" s="11" t="n">
-        <v>212016</v>
       </c>
       <c r="N32" s="11" t="n">
         <v>207011.6</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>210182.1</v>
+        <v>1009.3</v>
       </c>
       <c r="P32" s="11" t="n">
         <v>212017.7</v>
@@ -16557,16 +19539,16 @@
         <v>211017.2</v>
       </c>
       <c r="L33" s="11" t="n">
+        <v>211487.9</v>
+      </c>
+      <c r="M33" s="11" t="n">
         <v>212017.4</v>
-      </c>
-      <c r="M33" s="11" t="n">
-        <v>211015.1</v>
       </c>
       <c r="N33" s="11" t="n">
         <v>206012.5</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>210017.6</v>
+        <v>1004.9</v>
       </c>
       <c r="P33" s="11" t="n">
         <v>211019.5</v>
@@ -16595,16 +19577,16 @@
         <v>210182.1</v>
       </c>
       <c r="L34" s="11" t="n">
+        <v>211018.6</v>
+      </c>
+      <c r="M34" s="11" t="n">
         <v>211019.3</v>
-      </c>
-      <c r="M34" s="11" t="n">
-        <v>210015.7</v>
       </c>
       <c r="N34" s="11" t="n">
         <v>206009.4</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>210015.7</v>
+        <v>1004.4</v>
       </c>
       <c r="P34" s="11" t="n">
         <v>211017.9</v>
@@ -16633,16 +19615,16 @@
         <v>210017.8</v>
       </c>
       <c r="L35" s="11" t="n">
+        <v>211017</v>
+      </c>
+      <c r="M35" s="11" t="n">
         <v>211017.7</v>
-      </c>
-      <c r="M35" s="11" t="n">
-        <v>210014</v>
       </c>
       <c r="N35" s="11" t="n">
         <v>5008.2</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>209021.5</v>
+        <v>1004.8</v>
       </c>
       <c r="P35" s="11" t="n">
         <v>211016.9</v>
@@ -16671,16 +19653,16 @@
         <v>210016.1</v>
       </c>
       <c r="L36" s="11" t="n">
+        <v>210100.8</v>
+      </c>
+      <c r="M36" s="11" t="n">
         <v>211016.1</v>
-      </c>
-      <c r="M36" s="11" t="n">
-        <v>209016.3</v>
       </c>
       <c r="N36" s="11" t="n">
         <v>4008.5</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>209019.6</v>
+        <v>1004.1</v>
       </c>
       <c r="P36" s="11" t="n">
         <v>210017</v>
@@ -16709,16 +19691,16 @@
         <v>209022.2</v>
       </c>
       <c r="L37" s="11" t="n">
+        <v>210017.9</v>
+      </c>
+      <c r="M37" s="11" t="n">
         <v>210018.5</v>
-      </c>
-      <c r="M37" s="11" t="n">
-        <v>209014.8</v>
       </c>
       <c r="N37" s="11" t="n">
         <v>3006.7</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>209017.7</v>
+        <v>12005.5</v>
       </c>
       <c r="P37" s="11" t="n">
         <v>210015.4</v>
@@ -16747,16 +19729,16 @@
         <v>209020.5</v>
       </c>
       <c r="L38" s="11" t="n">
+        <v>210016.4</v>
+      </c>
+      <c r="M38" s="11" t="n">
         <v>210017</v>
-      </c>
-      <c r="M38" s="11" t="n">
-        <v>209013.5</v>
       </c>
       <c r="N38" s="11" t="n">
         <v>2011.9</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>209015.8</v>
+        <v>13003.3</v>
       </c>
       <c r="P38" s="11" t="n">
         <v>209809.1</v>
@@ -16785,16 +19767,16 @@
         <v>209018.8</v>
       </c>
       <c r="L39" s="11" t="n">
+        <v>209711.1</v>
+      </c>
+      <c r="M39" s="11" t="n">
         <v>210015.4</v>
-      </c>
-      <c r="M39" s="11" t="n">
-        <v>9011.6</v>
       </c>
       <c r="N39" s="11" t="n">
         <v>2008.9</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>209013.7</v>
+        <v>11001.8</v>
       </c>
       <c r="P39" s="11" t="n">
         <v>209012.5</v>
@@ -16823,16 +19805,16 @@
         <v>209017.1</v>
       </c>
       <c r="L40" s="11" t="n">
+        <v>209021.1</v>
+      </c>
+      <c r="M40" s="11" t="n">
         <v>209021.7</v>
-      </c>
-      <c r="M40" s="11" t="n">
-        <v>9010.299999999999</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>2005.8</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>208012.2</v>
+        <v>11001.6</v>
       </c>
       <c r="P40" s="11" t="n">
         <v>208013.2</v>
@@ -16861,16 +19843,16 @@
         <v>209015.3</v>
       </c>
       <c r="L41" s="11" t="n">
+        <v>209020.1</v>
+      </c>
+      <c r="M41" s="11" t="n">
         <v>209020.7</v>
-      </c>
-      <c r="M41" s="11" t="n">
-        <v>8011.5</v>
       </c>
       <c r="N41" s="11" t="n">
         <v>1009.4</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>207012.6</v>
+        <v>11003.1</v>
       </c>
       <c r="P41" s="11" t="n">
         <v>208011.6</v>
@@ -16899,16 +19881,16 @@
         <v>209013.3</v>
       </c>
       <c r="L42" s="11" t="n">
+        <v>209018.6</v>
+      </c>
+      <c r="M42" s="11" t="n">
         <v>209019.1</v>
-      </c>
-      <c r="M42" s="11" t="n">
-        <v>8009.8</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>207010.7</v>
+        <v>11001.3</v>
       </c>
       <c r="P42" s="11" t="n">
         <v>207014.4</v>
@@ -16937,16 +19919,16 @@
         <v>208012.2</v>
       </c>
       <c r="L43" s="11" t="n">
+        <v>209017</v>
+      </c>
+      <c r="M43" s="11" t="n">
         <v>209017.5</v>
-      </c>
-      <c r="M43" s="11" t="n">
-        <v>7355.4</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>1003.8</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>206012.7</v>
+        <v>11001.4</v>
       </c>
       <c r="P43" s="11" t="n">
         <v>207012.9</v>
@@ -16975,16 +19957,16 @@
         <v>207155.4</v>
       </c>
       <c r="L44" s="11" t="n">
+        <v>209015.5</v>
+      </c>
+      <c r="M44" s="11" t="n">
         <v>209016</v>
-      </c>
-      <c r="M44" s="11" t="n">
-        <v>7007.2</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>1004</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>206010.8</v>
+        <v>11002</v>
       </c>
       <c r="P44" s="11" t="n">
         <v>207011.3</v>
@@ -17013,16 +19995,16 @@
         <v>207011.1</v>
       </c>
       <c r="L45" s="11" t="n">
+        <v>208932.5</v>
+      </c>
+      <c r="M45" s="11" t="n">
         <v>209014.4</v>
-      </c>
-      <c r="M45" s="11" t="n">
-        <v>6008.9</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>1004.8</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>165192.7</v>
+        <v>11001.4</v>
       </c>
       <c r="P45" s="11" t="n">
         <v>206378.5</v>
@@ -17051,16 +20033,16 @@
         <v>206013.4</v>
       </c>
       <c r="L46" s="11" t="n">
+        <v>208014.2</v>
+      </c>
+      <c r="M46" s="11" t="n">
         <v>208014.6</v>
-      </c>
-      <c r="M46" s="11" t="n">
-        <v>6007.2</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>1004.6</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>5314.6</v>
+        <v>11001.7</v>
       </c>
       <c r="P46" s="11" t="n">
         <v>206010.3</v>
@@ -17089,16 +20071,16 @@
         <v>206011.7</v>
       </c>
       <c r="L47" s="11" t="n">
+        <v>208012.3</v>
+      </c>
+      <c r="M47" s="11" t="n">
         <v>208013</v>
-      </c>
-      <c r="M47" s="11" t="n">
-        <v>5108.6</v>
       </c>
       <c r="N47" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>4823.9</v>
+        <v>11001.9</v>
       </c>
       <c r="P47" s="11" t="n">
         <v>111661.6</v>
@@ -17127,16 +20109,16 @@
         <v>206010</v>
       </c>
       <c r="L48" s="11" t="n">
+        <v>207011.4</v>
+      </c>
+      <c r="M48" s="11" t="n">
         <v>207236</v>
-      </c>
-      <c r="M48" s="11" t="n">
-        <v>5005</v>
       </c>
       <c r="N48" s="11" t="n">
         <v>1005.1</v>
       </c>
       <c r="O48" s="11" t="n">
-        <v>4008.4</v>
+        <v>11001.4</v>
       </c>
       <c r="P48" s="11" t="n">
         <v>5006</v>
@@ -17165,16 +20147,16 @@
         <v>6008.9</v>
       </c>
       <c r="L49" s="11" t="n">
+        <v>206745.2</v>
+      </c>
+      <c r="M49" s="11" t="n">
         <v>207010.2</v>
-      </c>
-      <c r="M49" s="11" t="n">
-        <v>4011.7</v>
       </c>
       <c r="N49" s="11" t="n">
         <v>1006.9</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>4006.5</v>
+        <v>11002.8</v>
       </c>
       <c r="P49" s="11" t="n">
         <v>4700.4</v>
@@ -17203,16 +20185,16 @@
         <v>5008.4</v>
       </c>
       <c r="L50" s="11" t="n">
+        <v>206010.6</v>
+      </c>
+      <c r="M50" s="11" t="n">
         <v>206011</v>
-      </c>
-      <c r="M50" s="11" t="n">
-        <v>4010</v>
       </c>
       <c r="N50" s="11" t="n">
         <v>2005.4</v>
       </c>
       <c r="O50" s="11" t="n">
-        <v>3005.7</v>
+        <v>11003.9</v>
       </c>
       <c r="P50" s="11" t="n">
         <v>4008.8</v>
@@ -17241,16 +20223,16 @@
         <v>4437.2</v>
       </c>
       <c r="L51" s="11" t="n">
+        <v>206009.1</v>
+      </c>
+      <c r="M51" s="11" t="n">
         <v>206009.4</v>
-      </c>
-      <c r="M51" s="11" t="n">
-        <v>4008.3</v>
       </c>
       <c r="N51" s="11" t="n">
         <v>2004.6</v>
       </c>
       <c r="O51" s="11" t="n">
-        <v>2012.2</v>
+        <v>11001.5</v>
       </c>
       <c r="P51" s="11" t="n">
         <v>4007.2</v>
@@ -17279,16 +20261,16 @@
         <v>4008.4</v>
       </c>
       <c r="L52" s="11" t="n">
+        <v>205012</v>
+      </c>
+      <c r="M52" s="11" t="n">
         <v>205012.3</v>
-      </c>
-      <c r="M52" s="11" t="n">
-        <v>4006.6</v>
       </c>
       <c r="N52" s="11" t="n">
         <v>2005.9</v>
       </c>
       <c r="O52" s="11" t="n">
-        <v>2010.3</v>
+        <v>11001.9</v>
       </c>
       <c r="P52" s="11" t="n">
         <v>4005.6</v>
@@ -17317,16 +20299,16 @@
         <v>4006.7</v>
       </c>
       <c r="L53" s="11" t="n">
+        <v>205010.5</v>
+      </c>
+      <c r="M53" s="11" t="n">
         <v>205010.8</v>
-      </c>
-      <c r="M53" s="11" t="n">
-        <v>4005</v>
       </c>
       <c r="N53" s="11" t="n">
         <v>2006.3</v>
       </c>
       <c r="O53" s="11" t="n">
-        <v>2008.3</v>
+        <v>12004.6</v>
       </c>
       <c r="P53" s="11" t="n">
         <v>4004</v>
@@ -17355,16 +20337,16 @@
         <v>3006.2</v>
       </c>
       <c r="L54" s="11" t="n">
+        <v>205009</v>
+      </c>
+      <c r="M54" s="11" t="n">
         <v>205009.2</v>
-      </c>
-      <c r="M54" s="11" t="n">
-        <v>3006.7</v>
       </c>
       <c r="N54" s="11" t="n">
         <v>2007.1</v>
       </c>
       <c r="O54" s="11" t="n">
-        <v>2006.4</v>
+        <v>11002.4</v>
       </c>
       <c r="P54" s="11" t="n">
         <v>3003.6</v>
@@ -17393,16 +20375,16 @@
         <v>2033.1</v>
       </c>
       <c r="L55" s="11" t="n">
+        <v>204009.7</v>
+      </c>
+      <c r="M55" s="11" t="n">
         <v>204376.5</v>
-      </c>
-      <c r="M55" s="11" t="n">
-        <v>3005</v>
       </c>
       <c r="N55" s="11" t="n">
         <v>2005.8</v>
       </c>
       <c r="O55" s="11" t="n">
-        <v>2004.5</v>
+        <v>11002.1</v>
       </c>
       <c r="P55" s="11" t="n">
         <v>2012</v>
@@ -17431,16 +20413,16 @@
         <v>2011.1</v>
       </c>
       <c r="L56" s="11" t="n">
+        <v>204008.2</v>
+      </c>
+      <c r="M56" s="11" t="n">
         <v>204008.4</v>
-      </c>
-      <c r="M56" s="11" t="n">
-        <v>3003.3</v>
       </c>
       <c r="N56" s="11" t="n">
         <v>2007.8</v>
       </c>
       <c r="O56" s="11" t="n">
-        <v>1009.2</v>
+        <v>11003.3</v>
       </c>
       <c r="P56" s="11" t="n">
         <v>2010.4</v>
@@ -17469,16 +20451,16 @@
         <v>2009.4</v>
       </c>
       <c r="L57" s="11" t="n">
+        <v>76843.10000000001</v>
+      </c>
+      <c r="M57" s="11" t="n">
         <v>142476.1</v>
-      </c>
-      <c r="M57" s="11" t="n">
-        <v>2005.6</v>
       </c>
       <c r="N57" s="11" t="n">
         <v>2007.1</v>
       </c>
       <c r="O57" s="11" t="n">
-        <v>1007.5</v>
+        <v>11001.4</v>
       </c>
       <c r="P57" s="11" t="n">
         <v>2008.8</v>
@@ -17510,13 +20492,13 @@
         <v>3004</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>2003.9</v>
+        <v>3004</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>2007.3</v>
       </c>
       <c r="O58" s="11" t="n">
-        <v>1005.7</v>
+        <v>11002</v>
       </c>
       <c r="P58" s="11" t="n">
         <v>2007.5</v>
@@ -17545,16 +20527,16 @@
         <v>2006</v>
       </c>
       <c r="L59" s="11" t="n">
+        <v>2779.6</v>
+      </c>
+      <c r="M59" s="11" t="n">
         <v>3003</v>
-      </c>
-      <c r="M59" s="11" t="n">
-        <v>2002.2</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>2006.4</v>
       </c>
       <c r="O59" s="11" t="n">
-        <v>1004</v>
+        <v>11002.6</v>
       </c>
       <c r="P59" s="11" t="n">
         <v>2006.1</v>
@@ -17583,16 +20565,16 @@
         <v>2004.3</v>
       </c>
       <c r="L60" s="11" t="n">
+        <v>2006.9</v>
+      </c>
+      <c r="M60" s="11" t="n">
         <v>2007.1</v>
-      </c>
-      <c r="M60" s="11" t="n">
-        <v>1008.9</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>2007.9</v>
       </c>
       <c r="O60" s="11" t="n">
-        <v>1006.5</v>
+        <v>11001.3</v>
       </c>
       <c r="P60" s="11" t="n">
         <v>2004.5</v>
@@ -17621,16 +20603,16 @@
         <v>1009.2</v>
       </c>
       <c r="L61" s="11" t="n">
+        <v>2005.4</v>
+      </c>
+      <c r="M61" s="11" t="n">
         <v>2005.5</v>
-      </c>
-      <c r="M61" s="11" t="n">
-        <v>1007.2</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>2005.2</v>
       </c>
       <c r="O61" s="11" t="n">
-        <v>1007.3</v>
+        <v>11002.9</v>
       </c>
       <c r="P61" s="11" t="n">
         <v>2002.9</v>
@@ -17662,13 +20644,13 @@
         <v>2003.9</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>1005.5</v>
+        <v>2003.9</v>
       </c>
       <c r="N62" s="11" t="n">
         <v>2002.9</v>
       </c>
       <c r="O62" s="11" t="n">
-        <v>1006.5</v>
+        <v>11008.3</v>
       </c>
       <c r="P62" s="11" t="n">
         <v>1005.3</v>
@@ -17697,16 +20679,16 @@
         <v>1006.1</v>
       </c>
       <c r="L63" s="11" t="n">
+        <v>2002.3</v>
+      </c>
+      <c r="M63" s="11" t="n">
         <v>2002.4</v>
-      </c>
-      <c r="M63" s="11" t="n">
-        <v>1003.8</v>
       </c>
       <c r="N63" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O63" s="11" t="n">
-        <v>1004.5</v>
+        <v>11005.2</v>
       </c>
       <c r="P63" s="11" t="n">
         <v>1003.7</v>
@@ -17738,13 +20720,13 @@
         <v>1002</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>1002.1</v>
+        <v>1002</v>
       </c>
       <c r="N64" s="11" t="n">
         <v>1003.5</v>
       </c>
       <c r="O64" s="11" t="n">
-        <v>1002.1</v>
+        <v>18864.8</v>
       </c>
       <c r="P64" s="11" t="n">
         <v>1002.1</v>
@@ -17782,7 +20764,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="11" t="n">
-        <v>0</v>
+        <v>11004</v>
       </c>
       <c r="P65" s="11" t="n">
         <v>0</v>

--- a/Kq_Thuật_toán_AI_Bảng.xlsx
+++ b/Kq_Thuật_toán_AI_Bảng.xlsx
@@ -1570,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U435"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1636,37 +1636,37 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 294.98 ms</t>
+          <t>Thời gian: 300.84 ms</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 437.49 ms</t>
+          <t>Thời gian: 468.04 ms</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 394.58 ms</t>
+          <t>Thời gian: 500.37 ms</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 261.58 ms</t>
+          <t>Thời gian: 308.1 ms</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 705.63 ms</t>
+          <t>Thời gian: 848.38 ms</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 652.48 ms</t>
+          <t>Thời gian: 513.06 ms</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian: 280.47 ms</t>
+          <t>Thời gian: 285.96 ms</t>
         </is>
       </c>
     </row>
@@ -2911,22 +2911,22 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>216024.7519830532</v>
+        <v>216024.2017392527</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>216024.7519830532</v>
+        <v>216024.2017392527</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>14</v>
@@ -2994,14 +2994,14 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>216024.2015556349</v>
+        <v>216023.6512298374</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L19" s="4" t="n">
@@ -3069,11 +3069,11 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>216023.6512298374</v>
+        <v>216023.1007778175</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>16</v>
@@ -3148,11 +3148,11 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>216023.1007778175</v>
+        <v>216022.55055</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>17</v>
@@ -3227,18 +3227,18 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>216022.55055</v>
+        <v>216022</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>216022</v>
+        <v>215022.1011</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>19</v>
@@ -3385,18 +3385,18 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>216022.1007778175</v>
+        <v>215021.55055</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
@@ -3464,18 +3464,18 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>216021.55055</v>
+        <v>215021</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L25" s="4" t="n">
@@ -3543,18 +3543,18 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>216021</v>
+        <v>215021.1007778175</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
@@ -3622,22 +3622,22 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>215021.65165</v>
+        <v>215020.55055</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>215022.7522677081</v>
+        <v>215021.65165</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>23</v>
@@ -3701,11 +3701,11 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>215021.1011</v>
+        <v>215020</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>24</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>215022.2017392527</v>
+        <v>215021.1011</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>24</v>
@@ -3780,22 +3780,22 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>215020.55055</v>
+        <v>214023.4031112698</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>215021.65165</v>
+        <v>215020.55055</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>25</v>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>215020</v>
+        <v>214022.85275</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>26</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>215021.1011</v>
+        <v>215020</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>26</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>214022.3022</v>
+        <v>214022.3023334524</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>215020.55055</v>
+        <v>214022.3022</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>27</v>
@@ -4017,22 +4017,22 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>214021.75165</v>
+        <v>214021.7519830532</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>215020</v>
+        <v>214021.75165</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>28</v>
@@ -4100,18 +4100,18 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>214021.2011</v>
+        <v>214021.2015556349</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>214022.3022</v>
+        <v>214021.2017392527</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>29</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I34" s="4" t="n">
@@ -4186,11 +4186,11 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>214021.7522677081</v>
+        <v>214020.6512298374</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>30</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>214020.1007778175</v>
+        <v>214020.1011</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>31</v>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="L35" s="4" t="n">
-        <v>214021.2017392527</v>
+        <v>214020.1007778175</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>31</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I36" s="4" t="n">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>214020.6512298374</v>
+        <v>214019.55055</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>32</v>
@@ -4423,11 +4423,11 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L37" s="4" t="n">
-        <v>214020.1007778175</v>
+        <v>214019</v>
       </c>
       <c r="M37" s="4" t="n">
         <v>33</v>
@@ -4502,11 +4502,11 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>214019.55055</v>
+        <v>213021.3023334524</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>34</v>
@@ -4581,11 +4581,11 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L39" s="4" t="n">
-        <v>214019</v>
+        <v>213020.7519830532</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>35</v>
@@ -4649,11 +4649,11 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>213020.2017392527</v>
+        <v>213020.2015556349</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>36</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>213021.3023334524</v>
+        <v>213020.2015556349</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>36</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L41" s="4" t="n">
-        <v>213020.7519830532</v>
+        <v>213019.6512298374</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>37</v>
@@ -4807,22 +4807,22 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>213019.1007778175</v>
+        <v>213019.1011</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>213020.2015556349</v>
+        <v>213019.1007778175</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>38</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L43" s="4" t="n">
-        <v>213019.6512298374</v>
+        <v>213018.55055</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>39</v>
@@ -4976,11 +4976,11 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>213019.1007778175</v>
+        <v>213018</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>40</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="L45" s="4" t="n">
-        <v>213018.55055</v>
+        <v>212020.3024596748</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>41</v>
@@ -5134,11 +5134,11 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>213018</v>
+        <v>212019.7519830532</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>42</v>
@@ -5213,11 +5213,11 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L47" s="4" t="n">
-        <v>212020.3024596748</v>
+        <v>212019.2017392527</v>
       </c>
       <c r="M47" s="4" t="n">
         <v>43</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>212019.7519830532</v>
+        <v>212018.6512298374</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>44</v>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="L49" s="4" t="n">
-        <v>212019.2017392527</v>
+        <v>212018.1011</v>
       </c>
       <c r="M49" s="4" t="n">
         <v>45</v>
@@ -5450,11 +5450,11 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>212018.65165</v>
+        <v>212017.55055</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>46</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="L51" s="4" t="n">
-        <v>212018.1011</v>
+        <v>212017</v>
       </c>
       <c r="M51" s="4" t="n">
         <v>47</v>
@@ -5608,11 +5608,11 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>212017.55055</v>
+        <v>211019.85275</v>
       </c>
       <c r="M52" s="4" t="n">
         <v>48</v>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="L53" s="4" t="n">
-        <v>212017</v>
+        <v>211019.3023334524</v>
       </c>
       <c r="M53" s="4" t="n">
         <v>49</v>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>211019.85275</v>
+        <v>211018.7519830532</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>50</v>
@@ -5845,11 +5845,11 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L55" s="4" t="n">
-        <v>211019.3023334524</v>
+        <v>211018.2015556349</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>51</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I56" s="4" t="n">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>211018.7519830532</v>
+        <v>211017.6512298374</v>
       </c>
       <c r="M56" s="4" t="n">
         <v>52</v>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -6003,11 +6003,11 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L57" s="4" t="n">
-        <v>211018.2015556349</v>
+        <v>211017.1011</v>
       </c>
       <c r="M57" s="4" t="n">
         <v>53</v>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>211017.6512298374</v>
+        <v>211016.55055</v>
       </c>
       <c r="M58" s="4" t="n">
         <v>54</v>
@@ -6161,11 +6161,11 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L59" s="4" t="n">
-        <v>211017.1007778175</v>
+        <v>211016</v>
       </c>
       <c r="M59" s="4" t="n">
         <v>55</v>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>211016.55055</v>
+        <v>210019.4031112698</v>
       </c>
       <c r="M60" s="4" t="n">
         <v>56</v>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -6319,11 +6319,11 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>211016</v>
+        <v>210018.85275</v>
       </c>
       <c r="M61" s="4" t="n">
         <v>57</v>
@@ -6391,18 +6391,18 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>210018.3024596748</v>
+        <v>210018.3023334524</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>210019.4031112698</v>
+        <v>210018.3023334524</v>
       </c>
       <c r="M62" s="4" t="n">
         <v>58</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6477,11 +6477,11 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L63" s="4" t="n">
-        <v>210018.85275</v>
+        <v>210017.7519830532</v>
       </c>
       <c r="M63" s="4" t="n">
         <v>59</v>
@@ -6545,11 +6545,11 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>210017.2015556349</v>
+        <v>210017.2017392527</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>60</v>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>210018.3023334524</v>
+        <v>210017.2017392527</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>60</v>
@@ -6635,11 +6635,11 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L65" s="4" t="n">
-        <v>210017.7519830532</v>
+        <v>210016.65165</v>
       </c>
       <c r="M65" s="4" t="n">
         <v>61</v>
@@ -6707,18 +6707,18 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>210016.1011</v>
+        <v>210016.1007778175</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>62</v>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>210017.2015556349</v>
+        <v>210016.1011</v>
       </c>
       <c r="M66" s="4" t="n">
         <v>62</v>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
@@ -6793,11 +6793,11 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L67" s="4" t="n">
-        <v>210016.6512298374</v>
+        <v>210015.55055</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>63</v>
@@ -6872,11 +6872,11 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>210016.1011</v>
+        <v>210015</v>
       </c>
       <c r="M68" s="4" t="n">
         <v>64</v>
@@ -6951,11 +6951,11 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L69" s="4" t="n">
-        <v>210015.55055</v>
+        <v>209022.2572341205</v>
       </c>
       <c r="M69" s="4" t="n">
         <v>65</v>
@@ -7030,11 +7030,11 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>210015</v>
+        <v>209021.7071711227</v>
       </c>
       <c r="M70" s="4" t="n">
         <v>66</v>
@@ -7098,11 +7098,11 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>209021.156622877</v>
+        <v>209021.7062709648</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>67</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="L71" s="4" t="n">
-        <v>209022.2572341205</v>
+        <v>209021.156622877</v>
       </c>
       <c r="M71" s="4" t="n">
         <v>67</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>209020.6060749486</v>
+        <v>209021.1557421686</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>68</v>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>209021.7071711227</v>
+        <v>209021.1557421686</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>68</v>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -7267,11 +7267,11 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L73" s="4" t="n">
-        <v>209021.7062709648</v>
+        <v>209020.6052177582</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>69</v>
@@ -7335,11 +7335,11 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>209020.0546992021</v>
+        <v>209020.0550707495</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>70</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>209021.156149187</v>
+        <v>209020.0550707495</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>70</v>
@@ -7418,18 +7418,18 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>209019.5045354162</v>
+        <v>209019.5049804618</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>71</v>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L75" s="4" t="n">
-        <v>209020.6060749486</v>
+        <v>209019.5045354162</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>71</v>
@@ -7493,11 +7493,11 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>209018.9540040604</v>
+        <v>209018.95495</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>72</v>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>209020.0555274316</v>
+        <v>209018.9540040604</v>
       </c>
       <c r="M76" s="4" t="n">
         <v>72</v>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>209018.4034785054</v>
+        <v>209018.4044</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>73</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="L77" s="4" t="n">
-        <v>209019.5049804618</v>
+        <v>209018.4034785054</v>
       </c>
       <c r="M77" s="4" t="n">
         <v>73</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>209017.8529618406</v>
+        <v>209017.85385</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>74</v>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>209018.95495</v>
+        <v>209017.8533455194</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>74</v>
@@ -7730,22 +7730,22 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>209017.3028044607</v>
+        <v>209017.3033</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>75</v>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L79" s="4" t="n">
-        <v>209018.4044</v>
+        <v>209017.3033</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>75</v>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I80" s="4" t="n">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>209017.85385</v>
+        <v>209016.75275</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>76</v>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="L81" s="4" t="n">
-        <v>209017.3033</v>
+        <v>209016.2022</v>
       </c>
       <c r="M81" s="4" t="n">
         <v>77</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>209016.75275</v>
+        <v>209015.65165</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>78</v>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="L83" s="4" t="n">
-        <v>209016.2022</v>
+        <v>209015.1011</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>79</v>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>209015.65165</v>
+        <v>209014.55055</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>80</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="L85" s="4" t="n">
-        <v>209015.1011</v>
+        <v>209014</v>
       </c>
       <c r="M85" s="4" t="n">
         <v>81</v>
@@ -8294,11 +8294,11 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L86" s="4" t="n">
-        <v>209014.55055</v>
+        <v>208015.2015556349</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>82</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="L87" s="4" t="n">
-        <v>209014</v>
+        <v>208014.6512298374</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>83</v>
@@ -8441,22 +8441,22 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>208014.1007778175</v>
+        <v>208014.1011</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>84</v>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L88" s="4" t="n">
-        <v>208015.2015556349</v>
+        <v>208014.1011</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>84</v>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L89" s="4" t="n">
-        <v>208014.6512298374</v>
+        <v>208013.55055</v>
       </c>
       <c r="M89" s="4" t="n">
         <v>85</v>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="L90" s="4" t="n">
-        <v>208014.1007778175</v>
+        <v>208013</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>86</v>
@@ -8689,11 +8689,11 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L91" s="4" t="n">
-        <v>208013.55055</v>
+        <v>208012</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>87</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>208013</v>
+        <v>208011</v>
       </c>
       <c r="M92" s="4" t="n">
         <v>88</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="L93" s="4" t="n">
-        <v>208012</v>
+        <v>207011.65165</v>
       </c>
       <c r="M93" s="4" t="n">
         <v>89</v>
@@ -8926,11 +8926,11 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L94" s="4" t="n">
-        <v>208011</v>
+        <v>207011.1011</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>90</v>
@@ -9005,11 +9005,11 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L95" s="4" t="n">
-        <v>207011.65165</v>
+        <v>207010.55055</v>
       </c>
       <c r="M95" s="4" t="n">
         <v>91</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="L96" s="4" t="n">
-        <v>207011.1011</v>
+        <v>207010</v>
       </c>
       <c r="M96" s="4" t="n">
         <v>92</v>
@@ -9163,11 +9163,11 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L97" s="4" t="n">
-        <v>207010.55055</v>
+        <v>206011.7522677081</v>
       </c>
       <c r="M97" s="4" t="n">
         <v>93</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="L98" s="4" t="n">
-        <v>207010</v>
+        <v>206011.2017392527</v>
       </c>
       <c r="M98" s="4" t="n">
         <v>94</v>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>206010.6512298374</v>
+        <v>206010.65165</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>95</v>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L99" s="4" t="n">
-        <v>206011.7522677081</v>
+        <v>206010.6512298374</v>
       </c>
       <c r="M99" s="4" t="n">
         <v>95</v>
@@ -9393,18 +9393,18 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>206010.1007778175</v>
+        <v>206010.1011</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>96</v>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>206011.2017392527</v>
+        <v>206010.1011</v>
       </c>
       <c r="M100" s="4" t="n">
         <v>96</v>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
@@ -9479,11 +9479,11 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L101" s="4" t="n">
-        <v>206010.65165</v>
+        <v>206009.55055</v>
       </c>
       <c r="M101" s="4" t="n">
         <v>97</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>206010.1011</v>
+        <v>206009</v>
       </c>
       <c r="M102" s="4" t="n">
         <v>98</v>
@@ -9637,11 +9637,11 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L103" s="4" t="n">
-        <v>206009.55055</v>
+        <v>205012.4034785054</v>
       </c>
       <c r="M103" s="4" t="n">
         <v>99</v>
@@ -9705,22 +9705,22 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>205012.4031112698</v>
+        <v>205011.8529618406</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>206009</v>
+        <v>205011.8529618406</v>
       </c>
       <c r="M104" s="4" t="n">
         <v>100</v>
@@ -9784,22 +9784,22 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>205011.85275</v>
+        <v>205011.3024596748</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>101</v>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L105" s="4" t="n">
-        <v>205012.4034785054</v>
+        <v>205011.3024596748</v>
       </c>
       <c r="M105" s="4" t="n">
         <v>101</v>
@@ -9867,18 +9867,18 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>205011.3024596748</v>
+        <v>205010.7522677081</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>102</v>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>205012.4031112698</v>
+        <v>205010.7519830532</v>
       </c>
       <c r="M106" s="4" t="n">
         <v>102</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I107" s="4" t="n">
@@ -9953,11 +9953,11 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
-        <v>205011.85275</v>
+        <v>205010.2015556349</v>
       </c>
       <c r="M107" s="4" t="n">
         <v>103</v>
@@ -10025,18 +10025,18 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>205010.2015556349</v>
+        <v>205010.2017392527</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>104</v>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>205011.3024596748</v>
+        <v>205009.6512298374</v>
       </c>
       <c r="M108" s="4" t="n">
         <v>104</v>
@@ -10111,11 +10111,11 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>205010.7519830532</v>
+        <v>205009.1007778175</v>
       </c>
       <c r="M109" s="4" t="n">
         <v>105</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I110" s="4" t="n">
@@ -10190,11 +10190,11 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>205010.2017392527</v>
+        <v>205008.55055</v>
       </c>
       <c r="M110" s="4" t="n">
         <v>106</v>
@@ -10269,11 +10269,11 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L111" s="4" t="n">
-        <v>205009.6512298374</v>
+        <v>205008</v>
       </c>
       <c r="M111" s="4" t="n">
         <v>107</v>
@@ -10348,11 +10348,11 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>205009.1007778175</v>
+        <v>5008.100777817459</v>
       </c>
       <c r="M112" s="4" t="n">
         <v>108</v>
@@ -10427,11 +10427,11 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L113" s="4" t="n">
-        <v>205008.55055</v>
+        <v>5008.55055</v>
       </c>
       <c r="M113" s="4" t="n">
         <v>109</v>
@@ -10495,22 +10495,22 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>204009.2015556349</v>
+        <v>204009.2017392527</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>110</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>205008</v>
+        <v>5008</v>
       </c>
       <c r="M114" s="4" t="n">
         <v>110</v>
@@ -10585,11 +10585,11 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
-        <v>204009.7519830532</v>
+        <v>5007</v>
       </c>
       <c r="M115" s="4" t="n">
         <v>111</v>
@@ -10657,18 +10657,18 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>204008.1011</v>
+        <v>204008.1007778175</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>112</v>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>204009.2015556349</v>
+        <v>5006</v>
       </c>
       <c r="M116" s="4" t="n">
         <v>112</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I117" s="4" t="n">
@@ -10743,11 +10743,11 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L117" s="4" t="n">
-        <v>204008.6512298374</v>
+        <v>4007.75275</v>
       </c>
       <c r="M117" s="4" t="n">
         <v>113</v>
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>204008.1011</v>
+        <v>4007.752267708094</v>
       </c>
       <c r="M118" s="4" t="n">
         <v>114</v>
@@ -10901,11 +10901,11 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L119" s="4" t="n">
-        <v>204007.55055</v>
+        <v>4007.2022</v>
       </c>
       <c r="M119" s="4" t="n">
         <v>115</v>
@@ -10980,11 +10980,11 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>204007</v>
+        <v>4006.65165</v>
       </c>
       <c r="M120" s="4" t="n">
         <v>116</v>
@@ -11059,11 +11059,11 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>3006</v>
+        <v>4006.1011</v>
       </c>
       <c r="M121" s="4" t="n">
         <v>117</v>
@@ -11138,11 +11138,11 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>3005</v>
+        <v>4005.55055</v>
       </c>
       <c r="M122" s="4" t="n">
         <v>118</v>
@@ -11217,11 +11217,11 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L123" s="4" t="n">
-        <v>3004</v>
+        <v>4005</v>
       </c>
       <c r="M123" s="4" t="n">
         <v>119</v>
@@ -11296,11 +11296,11 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>3004.100777817459</v>
+        <v>4005.100777817459</v>
       </c>
       <c r="M124" s="4" t="n">
         <v>120</v>
@@ -11375,11 +11375,11 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L125" s="4" t="n">
-        <v>3003.55055</v>
+        <v>4004.55055</v>
       </c>
       <c r="M125" s="4" t="n">
         <v>121</v>
@@ -11443,22 +11443,22 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2007.503889087297</v>
+        <v>2007.503966106403</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>122</v>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>3003</v>
+        <v>4004</v>
       </c>
       <c r="M126" s="4" t="n">
         <v>122</v>
@@ -11537,7 +11537,7 @@
         </is>
       </c>
       <c r="L127" s="4" t="n">
-        <v>2008.054295637322</v>
+        <v>3003.55055</v>
       </c>
       <c r="M127" s="4" t="n">
         <v>123</v>
@@ -11612,11 +11612,11 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>2007.503889087297</v>
+        <v>3003</v>
       </c>
       <c r="M128" s="4" t="n">
         <v>124</v>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I129" s="4" t="n">
@@ -11691,11 +11691,11 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>2006.95352171833</v>
+        <v>2005.852961840644</v>
       </c>
       <c r="M129" s="4" t="n">
         <v>125</v>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I130" s="4" t="n">
@@ -11770,11 +11770,11 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>2006.403111269837</v>
+        <v>2005.302804460732</v>
       </c>
       <c r="M130" s="4" t="n">
         <v>126</v>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="I131" s="4" t="n">
@@ -11849,11 +11849,11 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>2005.85275</v>
+        <v>2004.752267708094</v>
       </c>
       <c r="M131" s="4" t="n">
         <v>127</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>2005.302333452378</v>
+        <v>2004.201739252713</v>
       </c>
       <c r="M132" s="4" t="n">
         <v>128</v>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>2004.751983053201</v>
+        <v>2003.651229837388</v>
       </c>
       <c r="M133" s="4" t="n">
         <v>129</v>
@@ -12086,11 +12086,11 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>2004.201555634919</v>
+        <v>2003.100777817459</v>
       </c>
       <c r="M134" s="4" t="n">
         <v>130</v>
@@ -12165,11 +12165,11 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>2003.651229837388</v>
+        <v>2002.55055</v>
       </c>
       <c r="M135" s="4" t="n">
         <v>131</v>
@@ -12244,11 +12244,11 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="L136" s="4" t="n">
-        <v>2003.100777817459</v>
+        <v>2002</v>
       </c>
       <c r="M136" s="4" t="n">
         <v>132</v>
@@ -12323,11 +12323,11 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>2002.55055</v>
+        <v>1002.651229837388</v>
       </c>
       <c r="M137" s="4" t="n">
         <v>133</v>
@@ -12391,11 +12391,11 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>1002.100777817459</v>
+        <v>1002.1011</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>134</v>
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>2002</v>
+        <v>1002.100777817459</v>
       </c>
       <c r="M138" s="4" t="n">
         <v>134</v>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="I139" s="4" t="n">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>1002.651229837388</v>
+        <v>1001.55055</v>
       </c>
       <c r="M139" s="4" t="n">
         <v>135</v>
@@ -12560,11 +12560,11 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>1002.1011</v>
+        <v>1001</v>
       </c>
       <c r="M140" s="4" t="n">
         <v>136</v>
@@ -12639,11 +12639,11 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>1001.55055</v>
+        <v>0</v>
       </c>
       <c r="M141" s="4" t="n">
         <v>137</v>
@@ -12702,17 +12702,6 @@
       <c r="F142" s="4" t="n">
         <v>1010</v>
       </c>
-      <c r="J142" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="n">
-        <v>1001</v>
-      </c>
       <c r="M142" s="4" t="n">
         <v>138</v>
       </c>
@@ -12770,17 +12759,6 @@
       <c r="F143" s="4" t="n">
         <v>1009.5</v>
       </c>
-      <c r="J143" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M143" s="4" t="n">
         <v>139</v>
       </c>
@@ -13375,7 +13353,7 @@
       </c>
       <c r="Q157" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R157" s="4" t="n">
@@ -13399,11 +13377,11 @@
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R158" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="159">
@@ -13427,7 +13405,7 @@
         </is>
       </c>
       <c r="R159" s="4" t="n">
-        <v>1004.5</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="160">
@@ -13447,7 +13425,7 @@
       </c>
       <c r="Q160" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R160" s="4" t="n">
@@ -13471,11 +13449,11 @@
       </c>
       <c r="Q161" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R161" s="4" t="n">
-        <v>1004.5</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="162">
@@ -13495,11 +13473,11 @@
       </c>
       <c r="Q162" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R162" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="163">
@@ -13543,11 +13521,11 @@
       </c>
       <c r="Q164" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R164" s="4" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="165">
@@ -13567,11 +13545,11 @@
       </c>
       <c r="Q165" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R165" s="4" t="n">
-        <v>1003.5</v>
+        <v>1004.5</v>
       </c>
     </row>
     <row r="166">
@@ -13591,11 +13569,11 @@
       </c>
       <c r="Q166" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R166" s="4" t="n">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="167">
@@ -13615,7 +13593,7 @@
       </c>
       <c r="Q167" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R167" s="4" t="n">
@@ -13663,7 +13641,7 @@
       </c>
       <c r="Q169" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R169" s="4" t="n">
@@ -13687,11 +13665,11 @@
       </c>
       <c r="Q170" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R170" s="4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="171">
@@ -13711,11 +13689,11 @@
       </c>
       <c r="Q171" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R171" s="4" t="n">
-        <v>1004.5</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="172">
@@ -13735,11 +13713,11 @@
       </c>
       <c r="Q172" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R172" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="173">
@@ -13759,7 +13737,7 @@
       </c>
       <c r="Q173" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R173" s="4" t="n">
@@ -13783,11 +13761,11 @@
       </c>
       <c r="Q174" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R174" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="175">
@@ -13807,11 +13785,11 @@
       </c>
       <c r="Q175" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R175" s="4" t="n">
-        <v>1004.5</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="176">
@@ -13831,7 +13809,7 @@
       </c>
       <c r="Q176" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R176" s="4" t="n">
@@ -13855,7 +13833,7 @@
       </c>
       <c r="Q177" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R177" s="4" t="n">
@@ -13879,7 +13857,7 @@
       </c>
       <c r="Q178" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R178" s="4" t="n">
@@ -13907,7 +13885,7 @@
         </is>
       </c>
       <c r="R179" s="4" t="n">
-        <v>1004.5</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="180">
@@ -13927,11 +13905,11 @@
       </c>
       <c r="Q180" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R180" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="181">
@@ -13955,7 +13933,7 @@
         </is>
       </c>
       <c r="R181" s="4" t="n">
-        <v>1004.5</v>
+        <v>1006.2011</v>
       </c>
     </row>
     <row r="182">
@@ -13975,11 +13953,11 @@
       </c>
       <c r="Q182" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R182" s="4" t="n">
-        <v>1004</v>
+        <v>2005.55055</v>
       </c>
     </row>
     <row r="183">
@@ -14003,7 +13981,7 @@
         </is>
       </c>
       <c r="R183" s="4" t="n">
-        <v>1004.5</v>
+        <v>2006.1011</v>
       </c>
     </row>
     <row r="184">
@@ -14027,7 +14005,7 @@
         </is>
       </c>
       <c r="R184" s="4" t="n">
-        <v>12004</v>
+        <v>2006.65165</v>
       </c>
     </row>
     <row r="185">
@@ -14051,7 +14029,7 @@
         </is>
       </c>
       <c r="R185" s="4" t="n">
-        <v>12004.5005</v>
+        <v>2006.1011</v>
       </c>
     </row>
     <row r="186">
@@ -14071,11 +14049,11 @@
       </c>
       <c r="Q186" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R186" s="4" t="n">
-        <v>12005.001</v>
+        <v>2006.100777817459</v>
       </c>
     </row>
     <row r="187">
@@ -14095,11 +14073,11 @@
       </c>
       <c r="Q187" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R187" s="4" t="n">
-        <v>12005.5015</v>
+        <v>2006.1011</v>
       </c>
     </row>
     <row r="188">
@@ -14123,7 +14101,7 @@
         </is>
       </c>
       <c r="R188" s="4" t="n">
-        <v>12005.001</v>
+        <v>2006.65165</v>
       </c>
     </row>
     <row r="189">
@@ -14143,11 +14121,11 @@
       </c>
       <c r="Q189" s="4" t="inlineStr">
         <is>
-          <t>TRÁI</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R189" s="4" t="n">
-        <v>12005.5015</v>
+        <v>2007.2022</v>
       </c>
     </row>
     <row r="190">
@@ -14171,7 +14149,7 @@
         </is>
       </c>
       <c r="R190" s="4" t="n">
-        <v>12006.00158113883</v>
+        <v>2007.201739252713</v>
       </c>
     </row>
     <row r="191">
@@ -14191,11 +14169,11 @@
       </c>
       <c r="Q191" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R191" s="4" t="n">
-        <v>12005.5015</v>
+        <v>2007.75165</v>
       </c>
     </row>
     <row r="192">
@@ -14215,11 +14193,11 @@
       </c>
       <c r="Q192" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>LÊN</t>
         </is>
       </c>
       <c r="R192" s="4" t="n">
-        <v>12006.00158113883</v>
+        <v>2007.201739252713</v>
       </c>
     </row>
     <row r="193">
@@ -14239,11 +14217,11 @@
       </c>
       <c r="Q193" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R193" s="4" t="n">
-        <v>12006.50180277564</v>
+        <v>2006.651229837388</v>
       </c>
     </row>
     <row r="194">
@@ -14263,11 +14241,11 @@
       </c>
       <c r="Q194" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R194" s="4" t="n">
-        <v>13005</v>
+        <v>2006.100777817459</v>
       </c>
     </row>
     <row r="195">
@@ -14291,7 +14269,7 @@
         </is>
       </c>
       <c r="R195" s="4" t="n">
-        <v>13004</v>
+        <v>2005.55055</v>
       </c>
     </row>
     <row r="196">
@@ -14311,11 +14289,11 @@
       </c>
       <c r="Q196" s="4" t="inlineStr">
         <is>
-          <t>XUỐNG</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R196" s="4" t="n">
-        <v>13003</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="197">
@@ -14339,7 +14317,7 @@
         </is>
       </c>
       <c r="R197" s="4" t="n">
-        <v>12004.7519830532</v>
+        <v>1005.100777817459</v>
       </c>
     </row>
     <row r="198">
@@ -14359,11 +14337,11 @@
       </c>
       <c r="Q198" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>TRÁI</t>
         </is>
       </c>
       <c r="R198" s="4" t="n">
-        <v>12004.20155563492</v>
+        <v>1004.55055</v>
       </c>
     </row>
     <row r="199">
@@ -14383,11 +14361,11 @@
       </c>
       <c r="Q199" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R199" s="4" t="n">
-        <v>12003.65122983739</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="200">
@@ -14407,11 +14385,11 @@
       </c>
       <c r="Q200" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R200" s="4" t="n">
-        <v>12003.10077781746</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="201">
@@ -14431,11 +14409,11 @@
       </c>
       <c r="Q201" s="4" t="inlineStr">
         <is>
-          <t>PHẢI</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R201" s="4" t="n">
-        <v>12002.55055</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="202">
@@ -14455,11 +14433,11 @@
       </c>
       <c r="Q202" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R202" s="4" t="n">
-        <v>12002</v>
+        <v>1002.100777817459</v>
       </c>
     </row>
     <row r="203">
@@ -14483,7 +14461,7 @@
         </is>
       </c>
       <c r="R203" s="4" t="n">
-        <v>11002.50111803399</v>
+        <v>1001.55055</v>
       </c>
     </row>
     <row r="204">
@@ -14503,11 +14481,11 @@
       </c>
       <c r="Q204" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>XUỐNG</t>
         </is>
       </c>
       <c r="R204" s="4" t="n">
-        <v>11002.00070710678</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="205">
@@ -14527,11 +14505,11 @@
       </c>
       <c r="Q205" s="4" t="inlineStr">
         <is>
-          <t>LÊN</t>
+          <t>PHẢI</t>
         </is>
       </c>
       <c r="R205" s="4" t="n">
-        <v>11001.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -14546,17 +14524,6 @@
       <c r="O206" s="4" t="n">
         <v>2005.1011</v>
       </c>
-      <c r="P206" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R206" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="207">
       <c r="M207" s="4" t="n">
@@ -14570,17 +14537,6 @@
       <c r="O207" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
-      <c r="P207" s="4" t="n">
-        <v>203</v>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R207" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="208">
       <c r="M208" s="4" t="n">
@@ -14594,17 +14550,6 @@
       <c r="O208" s="4" t="n">
         <v>2005.100777817459</v>
       </c>
-      <c r="P208" s="4" t="n">
-        <v>204</v>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R208" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="209">
       <c r="M209" s="4" t="n">
@@ -14618,17 +14563,6 @@
       <c r="O209" s="4" t="n">
         <v>2005.651229837388</v>
       </c>
-      <c r="P209" s="4" t="n">
-        <v>205</v>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R209" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
     </row>
     <row r="210">
       <c r="M210" s="4" t="n">
@@ -14642,17 +14576,6 @@
       <c r="O210" s="4" t="n">
         <v>2006.201555634919</v>
       </c>
-      <c r="P210" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="Q210" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R210" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="211">
       <c r="M211" s="4" t="n">
@@ -14666,17 +14589,6 @@
       <c r="O211" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
-      <c r="P211" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q211" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R211" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="212">
       <c r="M212" s="4" t="n">
@@ -14690,17 +14602,6 @@
       <c r="O212" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
-      <c r="P212" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="Q212" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R212" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="213">
       <c r="M213" s="4" t="n">
@@ -14714,17 +14615,6 @@
       <c r="O213" s="4" t="n">
         <v>2005.65165</v>
       </c>
-      <c r="P213" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="Q213" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R213" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="214">
       <c r="M214" s="4" t="n">
@@ -14738,17 +14628,6 @@
       <c r="O214" s="4" t="n">
         <v>2006.2022</v>
       </c>
-      <c r="P214" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q214" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R214" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="215">
       <c r="M215" s="4" t="n">
@@ -14762,17 +14641,6 @@
       <c r="O215" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
-      <c r="P215" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="Q215" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R215" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
     </row>
     <row r="216">
       <c r="M216" s="4" t="n">
@@ -14786,17 +14654,6 @@
       <c r="O216" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
-      <c r="P216" s="4" t="n">
-        <v>212</v>
-      </c>
-      <c r="Q216" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R216" s="4" t="n">
-        <v>12004.2011</v>
-      </c>
     </row>
     <row r="217">
       <c r="M217" s="4" t="n">
@@ -14810,17 +14667,6 @@
       <c r="O217" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
-      <c r="P217" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="Q217" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R217" s="4" t="n">
-        <v>12003.65122983739</v>
-      </c>
     </row>
     <row r="218">
       <c r="M218" s="4" t="n">
@@ -14834,17 +14680,6 @@
       <c r="O218" s="4" t="n">
         <v>2007.302333452378</v>
       </c>
-      <c r="P218" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="Q218" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R218" s="4" t="n">
-        <v>12003.10077781746</v>
-      </c>
     </row>
     <row r="219">
       <c r="M219" s="4" t="n">
@@ -14858,17 +14693,6 @@
       <c r="O219" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
-      <c r="P219" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="Q219" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R219" s="4" t="n">
-        <v>12002.55055</v>
-      </c>
     </row>
     <row r="220">
       <c r="M220" s="4" t="n">
@@ -14882,17 +14706,6 @@
       <c r="O220" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
-      <c r="P220" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q220" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R220" s="4" t="n">
-        <v>12002</v>
-      </c>
     </row>
     <row r="221">
       <c r="M221" s="4" t="n">
@@ -14906,17 +14719,6 @@
       <c r="O221" s="4" t="n">
         <v>2005.65165</v>
       </c>
-      <c r="P221" s="4" t="n">
-        <v>217</v>
-      </c>
-      <c r="Q221" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R221" s="4" t="n">
-        <v>11003.50180277564</v>
-      </c>
     </row>
     <row r="222">
       <c r="M222" s="4" t="n">
@@ -14930,17 +14732,6 @@
       <c r="O222" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
-      <c r="P222" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="Q222" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R222" s="4" t="n">
-        <v>11003.00158113883</v>
-      </c>
     </row>
     <row r="223">
       <c r="M223" s="4" t="n">
@@ -14954,17 +14745,6 @@
       <c r="O223" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
-      <c r="P223" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="Q223" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R223" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
     </row>
     <row r="224">
       <c r="M224" s="4" t="n">
@@ -14978,17 +14758,6 @@
       <c r="O224" s="4" t="n">
         <v>2006.2022</v>
       </c>
-      <c r="P224" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="Q224" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R224" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="225">
       <c r="M225" s="4" t="n">
@@ -15002,17 +14771,6 @@
       <c r="O225" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
-      <c r="P225" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="Q225" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R225" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="226">
       <c r="M226" s="4" t="n">
@@ -15026,17 +14784,6 @@
       <c r="O226" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
-      <c r="P226" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="Q226" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R226" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="227">
       <c r="M227" s="4" t="n">
@@ -15050,17 +14797,6 @@
       <c r="O227" s="4" t="n">
         <v>2007.85275</v>
       </c>
-      <c r="P227" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="Q227" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R227" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="228">
       <c r="M228" s="4" t="n">
@@ -15074,17 +14810,6 @@
       <c r="O228" s="4" t="n">
         <v>2008.403111269837</v>
       </c>
-      <c r="P228" s="4" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q228" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R228" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="229">
       <c r="M229" s="4" t="n">
@@ -15098,17 +14823,6 @@
       <c r="O229" s="4" t="n">
         <v>2007.85275</v>
       </c>
-      <c r="P229" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="Q229" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R229" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="230">
       <c r="M230" s="4" t="n">
@@ -15122,17 +14836,6 @@
       <c r="O230" s="4" t="n">
         <v>2008.403207023542</v>
       </c>
-      <c r="P230" s="4" t="n">
-        <v>226</v>
-      </c>
-      <c r="Q230" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R230" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="231">
       <c r="M231" s="4" t="n">
@@ -15146,17 +14849,6 @@
       <c r="O231" s="4" t="n">
         <v>2007.852961840644</v>
       </c>
-      <c r="P231" s="4" t="n">
-        <v>227</v>
-      </c>
-      <c r="Q231" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R231" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="232">
       <c r="M232" s="4" t="n">
@@ -15170,17 +14862,6 @@
       <c r="O232" s="4" t="n">
         <v>2007.302804460732</v>
       </c>
-      <c r="P232" s="4" t="n">
-        <v>228</v>
-      </c>
-      <c r="Q232" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R232" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="233">
       <c r="M233" s="4" t="n">
@@ -15194,17 +14875,6 @@
       <c r="O233" s="4" t="n">
         <v>2006.75275</v>
       </c>
-      <c r="P233" s="4" t="n">
-        <v>229</v>
-      </c>
-      <c r="Q233" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R233" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="234">
       <c r="M234" s="4" t="n">
@@ -15218,17 +14888,6 @@
       <c r="O234" s="4" t="n">
         <v>2007.3033</v>
       </c>
-      <c r="P234" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="Q234" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R234" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="235">
       <c r="M235" s="4" t="n">
@@ -15242,17 +14901,6 @@
       <c r="O235" s="4" t="n">
         <v>2007.853345519392</v>
       </c>
-      <c r="P235" s="4" t="n">
-        <v>231</v>
-      </c>
-      <c r="Q235" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R235" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
     </row>
     <row r="236">
       <c r="M236" s="4" t="n">
@@ -15266,17 +14914,6 @@
       <c r="O236" s="4" t="n">
         <v>2008.403478505426</v>
       </c>
-      <c r="P236" s="4" t="n">
-        <v>232</v>
-      </c>
-      <c r="Q236" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R236" s="4" t="n">
-        <v>11002.001</v>
-      </c>
     </row>
     <row r="237">
       <c r="M237" s="4" t="n">
@@ -15290,17 +14927,6 @@
       <c r="O237" s="4" t="n">
         <v>2007.852961840644</v>
       </c>
-      <c r="P237" s="4" t="n">
-        <v>233</v>
-      </c>
-      <c r="Q237" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R237" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="238">
       <c r="M238" s="4" t="n">
@@ -15314,17 +14940,6 @@
       <c r="O238" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
-      <c r="P238" s="4" t="n">
-        <v>234</v>
-      </c>
-      <c r="Q238" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R238" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="239">
       <c r="M239" s="4" t="n">
@@ -15338,17 +14953,6 @@
       <c r="O239" s="4" t="n">
         <v>2007.85275</v>
       </c>
-      <c r="P239" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="Q239" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R239" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="240">
       <c r="M240" s="4" t="n">
@@ -15362,17 +14966,6 @@
       <c r="O240" s="4" t="n">
         <v>2007.302333452378</v>
       </c>
-      <c r="P240" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="Q240" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R240" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="241">
       <c r="M241" s="4" t="n">
@@ -15386,17 +14979,6 @@
       <c r="O241" s="4" t="n">
         <v>2006.751983053201</v>
       </c>
-      <c r="P241" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="Q241" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R241" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="242">
       <c r="M242" s="4" t="n">
@@ -15410,17 +14992,6 @@
       <c r="O242" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
-      <c r="P242" s="4" t="n">
-        <v>238</v>
-      </c>
-      <c r="Q242" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R242" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="243">
       <c r="M243" s="4" t="n">
@@ -15434,17 +15005,6 @@
       <c r="O243" s="4" t="n">
         <v>2006.75165</v>
       </c>
-      <c r="P243" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="Q243" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R243" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="244">
       <c r="M244" s="4" t="n">
@@ -15458,17 +15018,6 @@
       <c r="O244" s="4" t="n">
         <v>2006.201739252713</v>
       </c>
-      <c r="P244" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="Q244" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R244" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="245">
       <c r="M245" s="4" t="n">
@@ -15482,17 +15031,6 @@
       <c r="O245" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
-      <c r="P245" s="4" t="n">
-        <v>241</v>
-      </c>
-      <c r="Q245" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R245" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="246">
       <c r="M246" s="4" t="n">
@@ -15506,17 +15044,6 @@
       <c r="O246" s="4" t="n">
         <v>2007.3022</v>
       </c>
-      <c r="P246" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="Q246" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R246" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="247">
       <c r="M247" s="4" t="n">
@@ -15530,17 +15057,6 @@
       <c r="O247" s="4" t="n">
         <v>2006.752267708094</v>
       </c>
-      <c r="P247" s="4" t="n">
-        <v>243</v>
-      </c>
-      <c r="Q247" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R247" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="248">
       <c r="M248" s="4" t="n">
@@ -15554,17 +15070,6 @@
       <c r="O248" s="4" t="n">
         <v>2007.302459674775</v>
       </c>
-      <c r="P248" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="Q248" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R248" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="249">
       <c r="M249" s="4" t="n">
@@ -15578,17 +15083,6 @@
       <c r="O249" s="4" t="n">
         <v>2007.85275</v>
       </c>
-      <c r="P249" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q249" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R249" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
     </row>
     <row r="250">
       <c r="M250" s="4" t="n">
@@ -15602,17 +15096,6 @@
       <c r="O250" s="4" t="n">
         <v>2008.403111269837</v>
       </c>
-      <c r="P250" s="4" t="n">
-        <v>246</v>
-      </c>
-      <c r="Q250" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R250" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="251">
       <c r="M251" s="4" t="n">
@@ -15626,17 +15109,6 @@
       <c r="O251" s="4" t="n">
         <v>2007.2011</v>
       </c>
-      <c r="P251" s="4" t="n">
-        <v>247</v>
-      </c>
-      <c r="Q251" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R251" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="252">
       <c r="M252" s="4" t="n">
@@ -15650,17 +15122,6 @@
       <c r="O252" s="4" t="n">
         <v>2006.651229837388</v>
       </c>
-      <c r="P252" s="4" t="n">
-        <v>248</v>
-      </c>
-      <c r="Q252" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R252" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="253">
       <c r="M253" s="4" t="n">
@@ -15674,17 +15135,6 @@
       <c r="O253" s="4" t="n">
         <v>2006.100777817459</v>
       </c>
-      <c r="P253" s="4" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q253" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R253" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="254">
       <c r="M254" s="4" t="n">
@@ -15698,17 +15148,6 @@
       <c r="O254" s="4" t="n">
         <v>2005.55055</v>
       </c>
-      <c r="P254" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="Q254" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R254" s="4" t="n">
-        <v>11002.001</v>
-      </c>
     </row>
     <row r="255">
       <c r="M255" s="4" t="n">
@@ -15722,17 +15161,6 @@
       <c r="O255" s="4" t="n">
         <v>2005</v>
       </c>
-      <c r="P255" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="Q255" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R255" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="256">
       <c r="M256" s="4" t="n">
@@ -15746,17 +15174,6 @@
       <c r="O256" s="4" t="n">
         <v>2005.55055</v>
       </c>
-      <c r="P256" s="4" t="n">
-        <v>252</v>
-      </c>
-      <c r="Q256" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R256" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="257">
       <c r="M257" s="4" t="n">
@@ -15770,17 +15187,6 @@
       <c r="O257" s="4" t="n">
         <v>2005</v>
       </c>
-      <c r="P257" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="Q257" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R257" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="258">
       <c r="M258" s="4" t="n">
@@ -15794,17 +15200,6 @@
       <c r="O258" s="4" t="n">
         <v>2004</v>
       </c>
-      <c r="P258" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="Q258" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R258" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="259">
       <c r="M259" s="4" t="n">
@@ -15818,17 +15213,6 @@
       <c r="O259" s="4" t="n">
         <v>2003</v>
       </c>
-      <c r="P259" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q259" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R259" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="260">
       <c r="M260" s="4" t="n">
@@ -15842,17 +15226,6 @@
       <c r="O260" s="4" t="n">
         <v>2003.100777817459</v>
       </c>
-      <c r="P260" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="Q260" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R260" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="261">
       <c r="M261" s="4" t="n">
@@ -15866,17 +15239,6 @@
       <c r="O261" s="4" t="n">
         <v>2002.55055</v>
       </c>
-      <c r="P261" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="Q261" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R261" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="262">
       <c r="M262" s="4" t="n">
@@ -15890,17 +15252,6 @@
       <c r="O262" s="4" t="n">
         <v>2002</v>
       </c>
-      <c r="P262" s="4" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q262" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R262" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="263">
       <c r="M263" s="4" t="n">
@@ -15914,17 +15265,6 @@
       <c r="O263" s="4" t="n">
         <v>1008.155070749452</v>
       </c>
-      <c r="P263" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="Q263" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R263" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="264">
       <c r="M264" s="4" t="n">
@@ -15938,17 +15278,6 @@
       <c r="O264" s="4" t="n">
         <v>1007.604666904756</v>
       </c>
-      <c r="P264" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="Q264" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R264" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="265">
       <c r="M265" s="4" t="n">
@@ -15962,17 +15291,6 @@
       <c r="O265" s="4" t="n">
         <v>1007.054295637322</v>
       </c>
-      <c r="P265" s="4" t="n">
-        <v>261</v>
-      </c>
-      <c r="Q265" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R265" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="266">
       <c r="M266" s="4" t="n">
@@ -15986,17 +15304,6 @@
       <c r="O266" s="4" t="n">
         <v>1006.503889087297</v>
       </c>
-      <c r="P266" s="4" t="n">
-        <v>262</v>
-      </c>
-      <c r="Q266" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R266" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="267">
       <c r="M267" s="4" t="n">
@@ -16010,17 +15317,6 @@
       <c r="O267" s="4" t="n">
         <v>1005.953521718331</v>
       </c>
-      <c r="P267" s="4" t="n">
-        <v>263</v>
-      </c>
-      <c r="Q267" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R267" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="268">
       <c r="M268" s="4" t="n">
@@ -16034,17 +15330,6 @@
       <c r="O268" s="4" t="n">
         <v>1005.403111269837</v>
       </c>
-      <c r="P268" s="4" t="n">
-        <v>264</v>
-      </c>
-      <c r="Q268" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R268" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="269">
       <c r="M269" s="4" t="n">
@@ -16058,17 +15343,6 @@
       <c r="O269" s="4" t="n">
         <v>1004.85275</v>
       </c>
-      <c r="P269" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="Q269" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R269" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="270">
       <c r="M270" s="4" t="n">
@@ -16082,17 +15356,6 @@
       <c r="O270" s="4" t="n">
         <v>1004.302333452378</v>
       </c>
-      <c r="P270" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="Q270" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R270" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="271">
       <c r="M271" s="4" t="n">
@@ -16106,17 +15369,6 @@
       <c r="O271" s="4" t="n">
         <v>1003.751983053202</v>
       </c>
-      <c r="P271" s="4" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R271" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="272">
       <c r="M272" s="4" t="n">
@@ -16130,17 +15382,6 @@
       <c r="O272" s="4" t="n">
         <v>1003.201555634919</v>
       </c>
-      <c r="P272" s="4" t="n">
-        <v>268</v>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R272" s="4" t="n">
-        <v>11001</v>
-      </c>
     </row>
     <row r="273">
       <c r="M273" s="4" t="n">
@@ -16154,17 +15395,6 @@
       <c r="O273" s="4" t="n">
         <v>1002.651229837388</v>
       </c>
-      <c r="P273" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R273" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="274">
       <c r="M274" s="4" t="n">
@@ -16178,17 +15408,6 @@
       <c r="O274" s="4" t="n">
         <v>1002.100777817459</v>
       </c>
-      <c r="P274" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R274" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="275">
       <c r="M275" s="4" t="n">
@@ -16202,17 +15421,6 @@
       <c r="O275" s="4" t="n">
         <v>1001.55055</v>
       </c>
-      <c r="P275" s="4" t="n">
-        <v>271</v>
-      </c>
-      <c r="Q275" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R275" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
     </row>
     <row r="276">
       <c r="M276" s="4" t="n">
@@ -16226,17 +15434,6 @@
       <c r="O276" s="4" t="n">
         <v>1001</v>
       </c>
-      <c r="P276" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R276" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
     </row>
     <row r="277">
       <c r="M277" s="4" t="n">
@@ -16250,2071 +15447,57 @@
       <c r="O277" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P277" s="4" t="n">
-        <v>273</v>
-      </c>
-      <c r="Q277" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R277" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="P278" s="4" t="n">
-        <v>274</v>
-      </c>
-      <c r="Q278" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R278" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="P279" s="4" t="n">
-        <v>275</v>
-      </c>
-      <c r="Q279" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R279" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
+    </row>
+    <row r="278"/>
+    <row r="279"/>
     <row r="280">
-      <c r="P280" s="4" t="n">
-        <v>276</v>
-      </c>
-      <c r="Q280" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R280" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="P281" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="Q281" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R281" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="P282" s="4" t="n">
-        <v>278</v>
-      </c>
-      <c r="Q282" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R282" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="P283" s="4" t="n">
-        <v>279</v>
-      </c>
-      <c r="Q283" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R283" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="P284" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R284" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="P285" s="4" t="n">
-        <v>281</v>
-      </c>
-      <c r="Q285" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R285" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="P286" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q286" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R286" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="P287" s="4" t="n">
-        <v>283</v>
-      </c>
-      <c r="Q287" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R287" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="P288" s="4" t="n">
-        <v>284</v>
-      </c>
-      <c r="Q288" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R288" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="P289" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="Q289" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R289" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="P290" s="4" t="n">
-        <v>286</v>
-      </c>
-      <c r="Q290" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R290" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="P291" s="4" t="n">
-        <v>287</v>
-      </c>
-      <c r="Q291" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R291" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="P292" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="Q292" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R292" s="4" t="n">
-        <v>11003.00141421356</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="P293" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="Q293" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R293" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="P294" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R294" s="4" t="n">
-        <v>11003.00158113883</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="P295" s="4" t="n">
-        <v>291</v>
-      </c>
-      <c r="Q295" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R295" s="4" t="n">
-        <v>11002.5015</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="P296" s="4" t="n">
-        <v>292</v>
-      </c>
-      <c r="Q296" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R296" s="4" t="n">
-        <v>11003.00158113883</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="P297" s="4" t="n">
-        <v>293</v>
-      </c>
-      <c r="Q297" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R297" s="4" t="n">
-        <v>11003.50180277564</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="P298" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="Q298" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R298" s="4" t="n">
-        <v>11004.00223606798</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="P299" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R299" s="4" t="n">
-        <v>11003.50206155281</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="P300" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="Q300" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R300" s="4" t="n">
-        <v>11004.00223606798</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="P301" s="4" t="n">
-        <v>297</v>
-      </c>
-      <c r="Q301" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R301" s="4" t="n">
-        <v>11003.50206155281</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="P302" s="4" t="n">
-        <v>298</v>
-      </c>
-      <c r="Q302" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R302" s="4" t="n">
-        <v>11003.002</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="P303" s="4" t="n">
-        <v>299</v>
-      </c>
-      <c r="Q303" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R303" s="4" t="n">
-        <v>11002.5015</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="P304" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="Q304" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R304" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="P305" s="4" t="n">
-        <v>301</v>
-      </c>
-      <c r="Q305" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R305" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="P306" s="4" t="n">
-        <v>302</v>
-      </c>
-      <c r="Q306" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R306" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="P307" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R307" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="P308" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="Q308" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R308" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="P309" s="4" t="n">
-        <v>305</v>
-      </c>
-      <c r="Q309" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R309" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="P310" s="4" t="n">
-        <v>306</v>
-      </c>
-      <c r="Q310" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R310" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="P311" s="4" t="n">
-        <v>307</v>
-      </c>
-      <c r="Q311" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R311" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="P312" s="4" t="n">
-        <v>308</v>
-      </c>
-      <c r="Q312" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R312" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="P313" s="4" t="n">
-        <v>309</v>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R313" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="P314" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="Q314" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R314" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="P315" s="4" t="n">
-        <v>311</v>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R315" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="P316" s="4" t="n">
-        <v>312</v>
-      </c>
-      <c r="Q316" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R316" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="P317" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="Q317" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R317" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="P318" s="4" t="n">
-        <v>314</v>
-      </c>
-      <c r="Q318" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R318" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="P319" s="4" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q319" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R319" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="P320" s="4" t="n">
-        <v>316</v>
-      </c>
-      <c r="Q320" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R320" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="P321" s="4" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q321" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R321" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="P322" s="4" t="n">
-        <v>318</v>
-      </c>
-      <c r="Q322" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R322" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="P323" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="Q323" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R323" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="P324" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="Q324" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R324" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="P325" s="4" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q325" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R325" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="P326" s="4" t="n">
-        <v>322</v>
-      </c>
-      <c r="Q326" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R326" s="4" t="n">
-        <v>12004.2011</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="P327" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="Q327" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R327" s="4" t="n">
-        <v>12005.2011</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="P328" s="4" t="n">
-        <v>324</v>
-      </c>
-      <c r="Q328" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R328" s="4" t="n">
-        <v>12004.65122983739</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="P329" s="4" t="n">
-        <v>325</v>
-      </c>
-      <c r="Q329" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R329" s="4" t="n">
-        <v>12004.10077781746</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="P330" s="4" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R330" s="4" t="n">
-        <v>12003.55055</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="P331" s="4" t="n">
-        <v>327</v>
-      </c>
-      <c r="Q331" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R331" s="4" t="n">
-        <v>12003</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="P332" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="Q332" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R332" s="4" t="n">
-        <v>12002</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="P333" s="4" t="n">
-        <v>329</v>
-      </c>
-      <c r="Q333" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R333" s="4" t="n">
-        <v>11003.50180277564</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="P334" s="4" t="n">
-        <v>330</v>
-      </c>
-      <c r="Q334" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R334" s="4" t="n">
-        <v>11003.00158113883</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="P335" s="4" t="n">
-        <v>331</v>
-      </c>
-      <c r="Q335" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R335" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="P336" s="4" t="n">
-        <v>332</v>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R336" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="P337" s="4" t="n">
-        <v>333</v>
-      </c>
-      <c r="Q337" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R337" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="P338" s="4" t="n">
-        <v>334</v>
-      </c>
-      <c r="Q338" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R338" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="P339" s="4" t="n">
-        <v>335</v>
-      </c>
-      <c r="Q339" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R339" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="P340" s="4" t="n">
-        <v>336</v>
-      </c>
-      <c r="Q340" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R340" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="P341" s="4" t="n">
-        <v>337</v>
-      </c>
-      <c r="Q341" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R341" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="P342" s="4" t="n">
-        <v>338</v>
-      </c>
-      <c r="Q342" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R342" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="P343" s="4" t="n">
-        <v>339</v>
-      </c>
-      <c r="Q343" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R343" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="P344" s="4" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q344" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R344" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="P345" s="4" t="n">
-        <v>341</v>
-      </c>
-      <c r="Q345" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R345" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="P346" s="4" t="n">
-        <v>342</v>
-      </c>
-      <c r="Q346" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R346" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="P347" s="4" t="n">
-        <v>343</v>
-      </c>
-      <c r="Q347" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R347" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="P348" s="4" t="n">
-        <v>344</v>
-      </c>
-      <c r="Q348" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R348" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="P349" s="4" t="n">
-        <v>345</v>
-      </c>
-      <c r="Q349" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R349" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="P350" s="4" t="n">
-        <v>346</v>
-      </c>
-      <c r="Q350" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R350" s="4" t="n">
-        <v>11003.00141421356</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="P351" s="4" t="n">
-        <v>347</v>
-      </c>
-      <c r="Q351" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R351" s="4" t="n">
-        <v>11003.50180277564</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="P352" s="4" t="n">
-        <v>348</v>
-      </c>
-      <c r="Q352" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R352" s="4" t="n">
-        <v>11003.00158113883</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="P353" s="4" t="n">
-        <v>349</v>
-      </c>
-      <c r="Q353" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R353" s="4" t="n">
-        <v>11003.50180277564</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="P354" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q354" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R354" s="4" t="n">
-        <v>11003.00141421356</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="P355" s="4" t="n">
-        <v>351</v>
-      </c>
-      <c r="Q355" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R355" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="P356" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="Q356" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R356" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="P357" s="4" t="n">
-        <v>353</v>
-      </c>
-      <c r="Q357" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R357" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="P358" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="Q358" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R358" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="P359" s="4" t="n">
-        <v>355</v>
-      </c>
-      <c r="Q359" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R359" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="P360" s="4" t="n">
-        <v>356</v>
-      </c>
-      <c r="Q360" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R360" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="P361" s="4" t="n">
-        <v>357</v>
-      </c>
-      <c r="Q361" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R361" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="P362" s="4" t="n">
-        <v>358</v>
-      </c>
-      <c r="Q362" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R362" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="P363" s="4" t="n">
-        <v>359</v>
-      </c>
-      <c r="Q363" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R363" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="P364" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="Q364" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R364" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="P365" s="4" t="n">
-        <v>361</v>
-      </c>
-      <c r="Q365" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R365" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="P366" s="4" t="n">
-        <v>362</v>
-      </c>
-      <c r="Q366" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R366" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="P367" s="4" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q367" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R367" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="P368" s="4" t="n">
-        <v>364</v>
-      </c>
-      <c r="Q368" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R368" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="P369" s="4" t="n">
-        <v>365</v>
-      </c>
-      <c r="Q369" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R369" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="P370" s="4" t="n">
-        <v>366</v>
-      </c>
-      <c r="Q370" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R370" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="P371" s="4" t="n">
-        <v>367</v>
-      </c>
-      <c r="Q371" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R371" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="P372" s="4" t="n">
-        <v>368</v>
-      </c>
-      <c r="Q372" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R372" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="P373" s="4" t="n">
-        <v>369</v>
-      </c>
-      <c r="Q373" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R373" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="P374" s="4" t="n">
-        <v>370</v>
-      </c>
-      <c r="Q374" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R374" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="P375" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q375" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R375" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="P376" s="4" t="n">
-        <v>372</v>
-      </c>
-      <c r="Q376" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R376" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="P377" s="4" t="n">
-        <v>373</v>
-      </c>
-      <c r="Q377" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R377" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="P378" s="4" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q378" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R378" s="4" t="n">
-        <v>11003.00141421356</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="P379" s="4" t="n">
-        <v>375</v>
-      </c>
-      <c r="Q379" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R379" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="P380" s="4" t="n">
-        <v>376</v>
-      </c>
-      <c r="Q380" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R380" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="P381" s="4" t="n">
-        <v>377</v>
-      </c>
-      <c r="Q381" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R381" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="P382" s="4" t="n">
-        <v>378</v>
-      </c>
-      <c r="Q382" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R382" s="4" t="n">
-        <v>11002.00070710678</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="P383" s="4" t="n">
-        <v>379</v>
-      </c>
-      <c r="Q383" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R383" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="P384" s="4" t="n">
-        <v>380</v>
-      </c>
-      <c r="Q384" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R384" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="P385" s="4" t="n">
-        <v>381</v>
-      </c>
-      <c r="Q385" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R385" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="P386" s="4" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q386" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R386" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="P387" s="4" t="n">
-        <v>383</v>
-      </c>
-      <c r="Q387" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R387" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="P388" s="4" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q388" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R388" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="P389" s="4" t="n">
-        <v>385</v>
-      </c>
-      <c r="Q389" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R389" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="P390" s="4" t="n">
-        <v>386</v>
-      </c>
-      <c r="Q390" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R390" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="P391" s="4" t="n">
-        <v>387</v>
-      </c>
-      <c r="Q391" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R391" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="P392" s="4" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q392" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R392" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="P393" s="4" t="n">
-        <v>389</v>
-      </c>
-      <c r="Q393" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R393" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="P394" s="4" t="n">
-        <v>390</v>
-      </c>
-      <c r="Q394" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R394" s="4" t="n">
-        <v>11003.001</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="P395" s="4" t="n">
-        <v>391</v>
-      </c>
-      <c r="Q395" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R395" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="P396" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="Q396" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R396" s="4" t="n">
-        <v>11003.001</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="P397" s="4" t="n">
-        <v>393</v>
-      </c>
-      <c r="Q397" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R397" s="4" t="n">
-        <v>11002.50111803399</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="P398" s="4" t="n">
-        <v>394</v>
-      </c>
-      <c r="Q398" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R398" s="4" t="n">
-        <v>11002.001</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="P399" s="4" t="n">
-        <v>395</v>
-      </c>
-      <c r="Q399" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R399" s="4" t="n">
-        <v>11001.5005</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="P400" s="4" t="n">
-        <v>396</v>
-      </c>
-      <c r="Q400" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R400" s="4" t="n">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="P401" s="4" t="n">
-        <v>397</v>
-      </c>
-      <c r="Q401" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R401" s="4" t="n">
-        <v>11004.2011</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="P402" s="4" t="n">
-        <v>398</v>
-      </c>
-      <c r="Q402" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R402" s="4" t="n">
-        <v>11007.40077781746</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="P403" s="4" t="n">
-        <v>399</v>
-      </c>
-      <c r="Q403" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R403" s="4" t="n">
-        <v>11007.95122983739</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="P404" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q404" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R404" s="4" t="n">
-        <v>11007.4011</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="P405" s="4" t="n">
-        <v>401</v>
-      </c>
-      <c r="Q405" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R405" s="4" t="n">
-        <v>11008.4011</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="P406" s="4" t="n">
-        <v>402</v>
-      </c>
-      <c r="Q406" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R406" s="4" t="n">
-        <v>11005</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="P407" s="4" t="n">
-        <v>403</v>
-      </c>
-      <c r="Q407" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R407" s="4" t="n">
-        <v>11005.5005</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="P408" s="4" t="n">
-        <v>404</v>
-      </c>
-      <c r="Q408" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R408" s="4" t="n">
-        <v>11005</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="P409" s="4" t="n">
-        <v>405</v>
-      </c>
-      <c r="Q409" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R409" s="4" t="n">
-        <v>11005.5005</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="P410" s="4" t="n">
-        <v>406</v>
-      </c>
-      <c r="Q410" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R410" s="4" t="n">
-        <v>11006.00070710678</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="P411" s="4" t="n">
-        <v>407</v>
-      </c>
-      <c r="Q411" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R411" s="4" t="n">
-        <v>11005.5005</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="P412" s="4" t="n">
-        <v>408</v>
-      </c>
-      <c r="Q412" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R412" s="4" t="n">
-        <v>11005</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="P413" s="4" t="n">
-        <v>409</v>
-      </c>
-      <c r="Q413" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R413" s="4" t="n">
-        <v>11005.5005</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="P414" s="4" t="n">
-        <v>410</v>
-      </c>
-      <c r="Q414" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R414" s="4" t="n">
-        <v>11005</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="P415" s="4" t="n">
-        <v>411</v>
-      </c>
-      <c r="Q415" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R415" s="4" t="n">
-        <v>11006</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="P416" s="4" t="n">
-        <v>412</v>
-      </c>
-      <c r="Q416" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R416" s="4" t="n">
-        <v>11006.55055</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="P417" s="4" t="n">
-        <v>413</v>
-      </c>
-      <c r="Q417" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R417" s="4" t="n">
-        <v>11007.1011</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="P418" s="4" t="n">
-        <v>414</v>
-      </c>
-      <c r="Q418" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R418" s="4" t="n">
-        <v>22008.65165</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="P419" s="4" t="n">
-        <v>415</v>
-      </c>
-      <c r="Q419" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R419" s="4" t="n">
-        <v>22008.65122983739</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="P420" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="Q420" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R420" s="4" t="n">
-        <v>22008.10077781746</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="P421" s="4" t="n">
-        <v>417</v>
-      </c>
-      <c r="Q421" s="4" t="inlineStr">
-        <is>
-          <t>XUỐNG</t>
-        </is>
-      </c>
-      <c r="R421" s="4" t="n">
-        <v>22007.55055</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="P422" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="Q422" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R422" s="4" t="n">
-        <v>22007</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="P423" s="4" t="n">
-        <v>419</v>
-      </c>
-      <c r="Q423" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R423" s="4" t="n">
-        <v>11009.3022</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="P424" s="4" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q424" s="4" t="inlineStr">
-        <is>
-          <t>TRÁI</t>
-        </is>
-      </c>
-      <c r="R424" s="4" t="n">
-        <v>11008.75226770809</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="P425" s="4" t="n">
-        <v>421</v>
-      </c>
-      <c r="Q425" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R425" s="4" t="n">
-        <v>11008.20173925271</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="P426" s="4" t="n">
-        <v>422</v>
-      </c>
-      <c r="Q426" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R426" s="4" t="n">
-        <v>11007.65122983739</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="P427" s="4" t="n">
-        <v>423</v>
-      </c>
-      <c r="Q427" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R427" s="4" t="n">
-        <v>11007.10077781746</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="P428" s="4" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q428" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R428" s="4" t="n">
-        <v>11006.55055</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="P429" s="4" t="n">
-        <v>425</v>
-      </c>
-      <c r="Q429" s="4" t="inlineStr">
-        <is>
-          <t>PHẢI</t>
-        </is>
-      </c>
-      <c r="R429" s="4" t="n">
-        <v>11006</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="P430" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="Q430" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R430" s="4" t="n">
-        <v>11005</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="P431" s="4" t="n">
-        <v>427</v>
-      </c>
-      <c r="Q431" s="4" t="inlineStr">
-        <is>
-          <t>LÊN</t>
-        </is>
-      </c>
-      <c r="R431" s="4" t="n">
-        <v>11004</v>
-      </c>
-    </row>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434">
-      <c r="A434" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 143 bước (294.98 ms).</t>
-        </is>
-      </c>
-      <c r="D434" s="6" t="inlineStr">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 143 bước (300.84 ms).</t>
+        </is>
+      </c>
+      <c r="D280" s="6" t="inlineStr">
         <is>
           <t>✗ Thất bại: Bị kẹt tại đỉnh cục bộ 
 (H = 1003.0).</t>
         </is>
       </c>
-      <c r="G434" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 137 bước (394.58 ms).</t>
-        </is>
-      </c>
-      <c r="J434" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 139 bước (261.58 ms).</t>
-        </is>
-      </c>
-      <c r="M434" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 273 bước (705.63 ms).</t>
-        </is>
-      </c>
-      <c r="P434" s="6" t="inlineStr">
-        <is>
-          <t>✗ Thất bại: Bị kẹt tại đỉnh cục bộ 
-(H = 11004.0).</t>
-        </is>
-      </c>
-      <c r="S434" s="5" t="inlineStr">
-        <is>
-          <t>✓ Thành công: Phá đảo trong 143 bước (280.47 ms).</t>
-        </is>
-      </c>
-    </row>
-    <row r="435"/>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 137 bước (500.37 ms).</t>
+        </is>
+      </c>
+      <c r="J280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 137 bước (308.1 ms).</t>
+        </is>
+      </c>
+      <c r="M280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 273 bước (848.38 ms).</t>
+        </is>
+      </c>
+      <c r="P280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 201 bước (513.06 ms).</t>
+        </is>
+      </c>
+      <c r="S280" s="5" t="inlineStr">
+        <is>
+          <t>✓ Thành công: Phá đảo trong 143 bước (285.96 ms).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="G434:I435"/>
-    <mergeCell ref="J434:L435"/>
-    <mergeCell ref="M434:O435"/>
-    <mergeCell ref="P434:R435"/>
-    <mergeCell ref="A434:C435"/>
-    <mergeCell ref="D434:F435"/>
-    <mergeCell ref="S434:U435"/>
+    <mergeCell ref="D280:F281"/>
+    <mergeCell ref="A280:C281"/>
+    <mergeCell ref="G280:I281"/>
+    <mergeCell ref="P280:R281"/>
+    <mergeCell ref="J280:L281"/>
+    <mergeCell ref="S280:U281"/>
+    <mergeCell ref="M280:O281"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18477,7 +15660,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>294.98</v>
+        <v>300.84</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>143</v>
@@ -18517,7 +15700,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>437.49</v>
+        <v>468.04</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>152</v>
@@ -18557,7 +15740,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>394.58</v>
+        <v>500.37</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>137</v>
@@ -18597,10 +15780,10 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>261.58</v>
+        <v>308.1</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>431028</v>
@@ -18637,7 +15820,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>705.63</v>
+        <v>848.38</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>273</v>
@@ -18677,23 +15860,23 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>652.48</v>
+        <v>513.0599999999999</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>427</v>
+        <v>201</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>431028</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>11004</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>420024</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>✗ Thất bại (H=11004.0)</t>
+        <v>431028</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>✓ Thành công</t>
         </is>
       </c>
       <c r="H10" s="8" t="n"/>
@@ -18717,7 +15900,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>280.47</v>
+        <v>285.96</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>143</v>
@@ -18934,13 +16117,13 @@
         <v>270046.6</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>261842.5</v>
+        <v>270046.6</v>
       </c>
       <c r="N17" s="11" t="n">
         <v>228025.2</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>218024.2</v>
+        <v>228026</v>
       </c>
       <c r="P17" s="11" t="n">
         <v>245434.2</v>
@@ -18978,7 +16161,7 @@
         <v>217023.5</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>216022.3</v>
+        <v>218024.4</v>
       </c>
       <c r="P18" s="11" t="n">
         <v>228025.1</v>
@@ -19016,7 +16199,7 @@
         <v>216022.7</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>214022.8</v>
+        <v>216717.4</v>
       </c>
       <c r="P19" s="11" t="n">
         <v>218024.1</v>
@@ -19054,7 +16237,7 @@
         <v>215020.9</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>213020.8</v>
+        <v>216022.9</v>
       </c>
       <c r="P20" s="11" t="n">
         <v>217023.2</v>
@@ -19083,16 +16266,16 @@
         <v>216023.4</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>216024.8</v>
+        <v>216024.2</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>216024.7</v>
+        <v>216024.2</v>
       </c>
       <c r="N21" s="11" t="n">
         <v>214021.8</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>212018.9</v>
+        <v>215021.3</v>
       </c>
       <c r="P21" s="11" t="n">
         <v>216024.4</v>
@@ -19121,16 +16304,16 @@
         <v>215409.8</v>
       </c>
       <c r="L22" s="11" t="n">
+        <v>216022.7</v>
+      </c>
+      <c r="M22" s="11" t="n">
         <v>216023.2</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <v>216023.1</v>
       </c>
       <c r="N22" s="11" t="n">
         <v>213591.4</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>211017.5</v>
+        <v>214409.8</v>
       </c>
       <c r="P22" s="11" t="n">
         <v>216022.8</v>
@@ -19159,7 +16342,7 @@
         <v>215021.1</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>216022.1</v>
+        <v>215021.8</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>216022.1</v>
@@ -19168,7 +16351,7 @@
         <v>213018.6</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>210016.7</v>
+        <v>214021.4</v>
       </c>
       <c r="P23" s="11" t="n">
         <v>216021.9</v>
@@ -19197,16 +16380,16 @@
         <v>214206.5</v>
       </c>
       <c r="L24" s="11" t="n">
+        <v>215020.9</v>
+      </c>
+      <c r="M24" s="11" t="n">
         <v>215653.9</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>215328.3</v>
       </c>
       <c r="N24" s="11" t="n">
         <v>212018.3</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>209019.7</v>
+        <v>214019.1</v>
       </c>
       <c r="P24" s="11" t="n">
         <v>215021.5</v>
@@ -19235,16 +16418,16 @@
         <v>214021.8</v>
       </c>
       <c r="L25" s="11" t="n">
+        <v>214023.3</v>
+      </c>
+      <c r="M25" s="11" t="n">
         <v>215020.5</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>215021.4</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>211018.7</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>209014.9</v>
+        <v>213019.7</v>
       </c>
       <c r="P25" s="11" t="n">
         <v>214755.3</v>
@@ -19276,13 +16459,13 @@
         <v>214021.8</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>214653.5</v>
+        <v>214021.8</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>210304.1</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>207012.7</v>
+        <v>212020.3</v>
       </c>
       <c r="P26" s="11" t="n">
         <v>214021.1</v>
@@ -19314,13 +16497,13 @@
         <v>214020.2</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>214021.1</v>
+        <v>214020.2</v>
       </c>
       <c r="N27" s="11" t="n">
         <v>210016.5</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>206011.8</v>
+        <v>212018</v>
       </c>
       <c r="P27" s="11" t="n">
         <v>214019.5</v>
@@ -19352,13 +16535,13 @@
         <v>213469.2</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>214019.5</v>
+        <v>213469.2</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>209021.2</v>
       </c>
       <c r="O28" s="11" t="n">
-        <v>5436.9</v>
+        <v>211019.2</v>
       </c>
       <c r="P28" s="11" t="n">
         <v>213020.7</v>
@@ -19390,13 +16573,13 @@
         <v>213020</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>213020.8</v>
+        <v>213020</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>209018.2</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>4007.5</v>
+        <v>211016.9</v>
       </c>
       <c r="P29" s="11" t="n">
         <v>213019.1</v>
@@ -19428,13 +16611,13 @@
         <v>213018.5</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>213019.3</v>
+        <v>213018.5</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>209015.1</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>2012.3</v>
+        <v>210018.6</v>
       </c>
       <c r="P30" s="11" t="n">
         <v>213018.1</v>
@@ -19466,13 +16649,13 @@
         <v>212019.8</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>212468.2</v>
+        <v>212019.8</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>208012.3</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>2007.5</v>
+        <v>210016.4</v>
       </c>
       <c r="P31" s="11" t="n">
         <v>212019.3</v>
@@ -19504,13 +16687,13 @@
         <v>212018.2</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>212019</v>
+        <v>212018.2</v>
       </c>
       <c r="N32" s="11" t="n">
         <v>207011.6</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>1009.3</v>
+        <v>209021.9</v>
       </c>
       <c r="P32" s="11" t="n">
         <v>212017.7</v>
@@ -19542,13 +16725,13 @@
         <v>211487.9</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>212017.4</v>
+        <v>211487.9</v>
       </c>
       <c r="N33" s="11" t="n">
         <v>206012.5</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>1004.9</v>
+        <v>209019.7</v>
       </c>
       <c r="P33" s="11" t="n">
         <v>211019.5</v>
@@ -19580,13 +16763,13 @@
         <v>211018.6</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>211019.3</v>
+        <v>211018.6</v>
       </c>
       <c r="N34" s="11" t="n">
         <v>206009.4</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>1004.4</v>
+        <v>209017.4</v>
       </c>
       <c r="P34" s="11" t="n">
         <v>211017.9</v>
@@ -19618,13 +16801,13 @@
         <v>211017</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>211017.7</v>
+        <v>211017</v>
       </c>
       <c r="N35" s="11" t="n">
         <v>5008.2</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>1004.8</v>
+        <v>209015.1</v>
       </c>
       <c r="P35" s="11" t="n">
         <v>211016.9</v>
@@ -19656,13 +16839,13 @@
         <v>210100.8</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>211016.1</v>
+        <v>210100.8</v>
       </c>
       <c r="N36" s="11" t="n">
         <v>4008.5</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>1004.1</v>
+        <v>208971.2</v>
       </c>
       <c r="P36" s="11" t="n">
         <v>210017</v>
@@ -19694,13 +16877,13 @@
         <v>210017.9</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>210018.5</v>
+        <v>210017.9</v>
       </c>
       <c r="N37" s="11" t="n">
         <v>3006.7</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>12005.5</v>
+        <v>207868.4</v>
       </c>
       <c r="P37" s="11" t="n">
         <v>210015.4</v>
@@ -19732,13 +16915,13 @@
         <v>210016.4</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>210017</v>
+        <v>210016.4</v>
       </c>
       <c r="N38" s="11" t="n">
         <v>2011.9</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>13003.3</v>
+        <v>207011</v>
       </c>
       <c r="P38" s="11" t="n">
         <v>209809.1</v>
@@ -19770,13 +16953,13 @@
         <v>209711.1</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>210015.4</v>
+        <v>209711.1</v>
       </c>
       <c r="N39" s="11" t="n">
         <v>2008.9</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>11001.8</v>
+        <v>206012.7</v>
       </c>
       <c r="P39" s="11" t="n">
         <v>209012.5</v>
@@ -19805,16 +16988,16 @@
         <v>209017.1</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>209021.1</v>
+        <v>209021.7</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>209021.7</v>
+        <v>209021.2</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>2005.8</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>11001.6</v>
+        <v>206010.4</v>
       </c>
       <c r="P40" s="11" t="n">
         <v>208013.2</v>
@@ -19846,13 +17029,13 @@
         <v>209020.1</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>209020.7</v>
+        <v>209020.1</v>
       </c>
       <c r="N41" s="11" t="n">
         <v>1009.4</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>11003.1</v>
+        <v>6008.8</v>
       </c>
       <c r="P41" s="11" t="n">
         <v>208011.6</v>
@@ -19884,13 +17067,13 @@
         <v>209018.6</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>209019.1</v>
+        <v>209018.6</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>11001.3</v>
+        <v>5007.7</v>
       </c>
       <c r="P42" s="11" t="n">
         <v>207014.4</v>
@@ -19922,13 +17105,13 @@
         <v>209017</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>209017.5</v>
+        <v>209017</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>1003.8</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>11001.4</v>
+        <v>4008.9</v>
       </c>
       <c r="P43" s="11" t="n">
         <v>207012.9</v>
@@ -19960,13 +17143,13 @@
         <v>209015.5</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>209016</v>
+        <v>209015.5</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>1004</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>11002</v>
+        <v>4006.6</v>
       </c>
       <c r="P44" s="11" t="n">
         <v>207011.3</v>
@@ -19998,13 +17181,13 @@
         <v>208932.5</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>209014.4</v>
+        <v>208932.5</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>1004.8</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>11001.4</v>
+        <v>3005.6</v>
       </c>
       <c r="P45" s="11" t="n">
         <v>206378.5</v>
@@ -20036,13 +17219,13 @@
         <v>208014.2</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>208014.6</v>
+        <v>208014.2</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>1004.6</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>11001.7</v>
+        <v>2011.7</v>
       </c>
       <c r="P46" s="11" t="n">
         <v>206010.3</v>
@@ -20074,13 +17257,13 @@
         <v>208012.3</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>208013</v>
+        <v>208012.3</v>
       </c>
       <c r="N47" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>11001.9</v>
+        <v>2009.4</v>
       </c>
       <c r="P47" s="11" t="n">
         <v>111661.6</v>
@@ -20112,13 +17295,13 @@
         <v>207011.4</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>207236</v>
+        <v>207011.4</v>
       </c>
       <c r="N48" s="11" t="n">
         <v>1005.1</v>
       </c>
       <c r="O48" s="11" t="n">
-        <v>11001.4</v>
+        <v>2007.2</v>
       </c>
       <c r="P48" s="11" t="n">
         <v>5006</v>
@@ -20150,13 +17333,13 @@
         <v>206745.2</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>207010.2</v>
+        <v>206745.2</v>
       </c>
       <c r="N49" s="11" t="n">
         <v>1006.9</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>11002.8</v>
+        <v>2004.9</v>
       </c>
       <c r="P49" s="11" t="n">
         <v>4700.4</v>
@@ -20188,13 +17371,13 @@
         <v>206010.6</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>206011</v>
+        <v>206010.6</v>
       </c>
       <c r="N50" s="11" t="n">
         <v>2005.4</v>
       </c>
       <c r="O50" s="11" t="n">
-        <v>11003.9</v>
+        <v>1009.3</v>
       </c>
       <c r="P50" s="11" t="n">
         <v>4008.8</v>
@@ -20226,13 +17409,13 @@
         <v>206009.1</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>206009.4</v>
+        <v>206009.1</v>
       </c>
       <c r="N51" s="11" t="n">
         <v>2004.6</v>
       </c>
       <c r="O51" s="11" t="n">
-        <v>11001.5</v>
+        <v>1007.2</v>
       </c>
       <c r="P51" s="11" t="n">
         <v>4007.2</v>
@@ -20261,16 +17444,16 @@
         <v>4008.4</v>
       </c>
       <c r="L52" s="11" t="n">
-        <v>205012</v>
+        <v>205011.5</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>205012.3</v>
+        <v>205011.5</v>
       </c>
       <c r="N52" s="11" t="n">
         <v>2005.9</v>
       </c>
       <c r="O52" s="11" t="n">
-        <v>11001.9</v>
+        <v>1005.2</v>
       </c>
       <c r="P52" s="11" t="n">
         <v>4005.6</v>
@@ -20302,13 +17485,13 @@
         <v>205010.5</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>205010.8</v>
+        <v>205010</v>
       </c>
       <c r="N53" s="11" t="n">
         <v>2006.3</v>
       </c>
       <c r="O53" s="11" t="n">
-        <v>12004.6</v>
+        <v>1003.1</v>
       </c>
       <c r="P53" s="11" t="n">
         <v>4004</v>
@@ -20340,13 +17523,13 @@
         <v>205009</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>205009.2</v>
+        <v>205008.4</v>
       </c>
       <c r="N54" s="11" t="n">
         <v>2007.1</v>
       </c>
       <c r="O54" s="11" t="n">
-        <v>11002.4</v>
+        <v>1003.9</v>
       </c>
       <c r="P54" s="11" t="n">
         <v>3003.6</v>
@@ -20378,13 +17561,13 @@
         <v>204009.7</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>204376.5</v>
+        <v>5008.5</v>
       </c>
       <c r="N55" s="11" t="n">
         <v>2005.8</v>
       </c>
       <c r="O55" s="11" t="n">
-        <v>11002.1</v>
+        <v>1004</v>
       </c>
       <c r="P55" s="11" t="n">
         <v>2012</v>
@@ -20416,13 +17599,13 @@
         <v>204008.2</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>204008.4</v>
+        <v>5006.2</v>
       </c>
       <c r="N56" s="11" t="n">
         <v>2007.8</v>
       </c>
       <c r="O56" s="11" t="n">
-        <v>11003.3</v>
+        <v>1004</v>
       </c>
       <c r="P56" s="11" t="n">
         <v>2010.4</v>
@@ -20454,13 +17637,13 @@
         <v>76843.10000000001</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>142476.1</v>
+        <v>4007.4</v>
       </c>
       <c r="N57" s="11" t="n">
         <v>2007.1</v>
       </c>
       <c r="O57" s="11" t="n">
-        <v>11001.4</v>
+        <v>1003.1</v>
       </c>
       <c r="P57" s="11" t="n">
         <v>2008.8</v>
@@ -20492,13 +17675,13 @@
         <v>3004</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>3004</v>
+        <v>4005.9</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>2007.3</v>
       </c>
       <c r="O58" s="11" t="n">
-        <v>11002</v>
+        <v>1003.9</v>
       </c>
       <c r="P58" s="11" t="n">
         <v>2007.5</v>
@@ -20530,13 +17713,13 @@
         <v>2779.6</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>3003</v>
+        <v>4005</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>2006.4</v>
       </c>
       <c r="O59" s="11" t="n">
-        <v>11002.6</v>
+        <v>1004.2</v>
       </c>
       <c r="P59" s="11" t="n">
         <v>2006.1</v>
@@ -20568,13 +17751,13 @@
         <v>2006.9</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>2007.1</v>
+        <v>3003.5</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>2007.9</v>
       </c>
       <c r="O60" s="11" t="n">
-        <v>11001.3</v>
+        <v>2006.4</v>
       </c>
       <c r="P60" s="11" t="n">
         <v>2004.5</v>
@@ -20606,13 +17789,13 @@
         <v>2005.4</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>2005.5</v>
+        <v>2005.4</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>2005.2</v>
       </c>
       <c r="O61" s="11" t="n">
-        <v>11002.9</v>
+        <v>2007</v>
       </c>
       <c r="P61" s="11" t="n">
         <v>2002.9</v>
@@ -20650,7 +17833,7 @@
         <v>2002.9</v>
       </c>
       <c r="O62" s="11" t="n">
-        <v>11008.3</v>
+        <v>2006.8</v>
       </c>
       <c r="P62" s="11" t="n">
         <v>1005.3</v>
@@ -20682,13 +17865,13 @@
         <v>2002.3</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>2002.4</v>
+        <v>2002.3</v>
       </c>
       <c r="N63" s="11" t="n">
         <v>1006.6</v>
       </c>
       <c r="O63" s="11" t="n">
-        <v>11005.2</v>
+        <v>1209.2</v>
       </c>
       <c r="P63" s="11" t="n">
         <v>1003.7</v>
@@ -20726,7 +17909,7 @@
         <v>1003.5</v>
       </c>
       <c r="O64" s="11" t="n">
-        <v>18864.8</v>
+        <v>1002.1</v>
       </c>
       <c r="P64" s="11" t="n">
         <v>1002.1</v>
@@ -20764,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="11" t="n">
-        <v>11004</v>
+        <v>0</v>
       </c>
       <c r="P65" s="11" t="n">
         <v>0</v>
